--- a/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
@@ -726,7 +726,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2891
+</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">259
@@ -735,50 +740,45 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -817,7 +817,7 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
@@ -829,12 +829,12 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>132</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>125</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -868,7 +868,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4645
+</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>2651</t>
@@ -876,7 +881,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -916,7 +921,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -929,36 +934,38 @@
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">77
+990
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">223
+</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1839
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -988,13 +995,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1760
+          <t xml:space="preserve">760
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -1013,13 +1020,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3380
+          <t xml:space="preserve">389
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -1037,14 +1044,10 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>01400</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">12
@@ -1053,13 +1056,13 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -1070,38 +1073,37 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">042
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8261
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -1119,7 +1121,7 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
@@ -1129,19 +1131,19 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">9310
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1160,7 +1162,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2552
+          <t xml:space="preserve">3552
 </t>
         </is>
       </c>
@@ -1184,54 +1186,57 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1017
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
-</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671
+          <t xml:space="preserve">1771
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -1243,7 +1248,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1255,13 +1260,13 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -1273,25 +1278,25 @@
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1813
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1310,7 +1315,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3279
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -1328,62 +1333,60 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2131
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13189
+          <t xml:space="preserve">127219
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="n"/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -1401,13 +1404,13 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1425,7 +1428,7 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
@@ -1437,7 +1440,7 @@
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -1457,7 +1460,8 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1473,43 +1477,51 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>615</t>
+          <t xml:space="preserve">1342
+</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>616</t>
+          <t xml:space="preserve">08
+</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11289
-</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="n"/>
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>2844</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="n"/>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1082
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
@@ -1522,13 +1534,13 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">8929
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">056
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
@@ -1552,7 +1564,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
@@ -1564,7 +1576,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1580,31 +1592,29 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>1563</t>
-        </is>
-      </c>
+      <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>550</t>
+          <t xml:space="preserve">177
+</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1614,13 +1624,13 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1637,63 +1647,67 @@
 </t>
         </is>
       </c>
-      <c r="N10" s="3" t="n"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16379
+</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">430
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">541
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1914
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1901
 </t>
         </is>
       </c>
@@ -1705,7 +1719,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1724,113 +1738,127 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
-</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n"/>
+          <t xml:space="preserve">77871
+</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2531
+228548177
+</t>
+        </is>
+      </c>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1238
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">986
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>2213</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">16
 </t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11975
-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>017</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">986
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1817
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">895
-</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1846,67 +1874,63 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>041</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>418</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1789
+          <t xml:space="preserve">737
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">277275
+163
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -1918,19 +1942,19 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8589
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -1948,25 +1972,24 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">8850
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1985,19 +2008,20 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -2008,63 +2032,58 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">001
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>447</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n"/>
       <c r="Q13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">238
@@ -2073,16 +2092,16 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">192
 </t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">668
@@ -2091,7 +2110,7 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
@@ -2109,17 +2128,22 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -2136,7 +2160,7 @@
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -2148,117 +2172,123 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>4445</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3561
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9908
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9979
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2065
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">23
 </t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>1144</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">845
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -2278,13 +2308,13 @@
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -2296,13 +2326,14 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -2313,16 +2344,11 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">3252
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="inlineStr">
         <is>
           <t>44</t>
@@ -2330,20 +2356,25 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n"/>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184883
+</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">9226
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -2361,13 +2392,13 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -2378,12 +2409,12 @@
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>83</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2412,16 +2443,16 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
-      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1272
+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -2433,25 +2464,25 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">4236
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4819
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -2463,81 +2494,82 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="n"/>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n"/>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>121</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">9416
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>553</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>40948</t>
+          <t xml:space="preserve">1004
+</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">935
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2556,7 +2588,8 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t xml:space="preserve">2579
+</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2567,8 +2600,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2579,13 +2611,13 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">4891
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -2595,41 +2627,30 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
+      <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>222</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">034
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4381
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n"/>
       <c r="Q17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">237
@@ -2638,30 +2659,29 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>431</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">3130
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912
-</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -2673,7 +2693,7 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11909
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -2685,7 +2705,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -2711,30 +2731,31 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1397
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">98
 </t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -2746,7 +2767,8 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>03</t>
+          <t xml:space="preserve">93
+</t>
         </is>
       </c>
       <c r="L18" s="3" t="n"/>
@@ -2758,76 +2780,72 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9986
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">3
+</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>124</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7420
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="n"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">767
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>6340880</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2843,57 +2861,70 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9 85 2
+</t>
+        </is>
+      </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>214251</t>
+          <t xml:space="preserve">233
+</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n"/>
       <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="n"/>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
+      <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -2904,13 +2935,12 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -2922,7 +2952,7 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>195</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -2933,13 +2963,13 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2971,22 +3001,17 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1106
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n"/>
       <c r="H20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">93
@@ -2995,7 +3020,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -3007,24 +3032,24 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -3036,58 +3061,53 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>131</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1912
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="n"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>432</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -3113,12 +3133,13 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>372</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -3130,7 +3151,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3142,102 +3163,102 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">32
+</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1266
+</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">809
-</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
-      <c r="V21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -3257,7 +3278,8 @@
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3268,64 +3290,65 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1906
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n"/>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">2121
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">165
 </t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11888
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n"/>
+          <t xml:space="preserve">1060
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">246
@@ -3340,49 +3363,49 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2891
+</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1892
+</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">329
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="V22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">889
-</t>
-        </is>
-      </c>
-      <c r="W22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
@@ -3413,25 +3436,25 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -3455,30 +3478,36 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n"/>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9700
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">066
+</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3491,14 +3520,13 @@
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3280
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
@@ -3515,7 +3543,8 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t xml:space="preserve">261
+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -3526,7 +3555,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>763</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3542,30 +3571,29 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1256
-</t>
-        </is>
-      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>531</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -3576,15 +3604,14 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7017
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -3595,17 +3622,16 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="n"/>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">044
-</t>
-        </is>
-      </c>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n"/>
       <c r="Q24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">231
@@ -3614,55 +3640,54 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">3281
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">1891
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1731
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>9300407</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -3680,55 +3705,41 @@
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
+      <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t xml:space="preserve">122 1
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n"/>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">372
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -3739,69 +3750,48 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="n"/>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111561
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="n"/>
+      <c r="S25" s="3" t="n"/>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="n"/>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="V25" s="3" t="n"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="n"/>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4158
+41419
+</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="n"/>
+      <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -3815,68 +3805,64 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
+      <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n"/>
+          <t xml:space="preserve">115178685
+1149791
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">08
 </t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="K26" s="3" t="n"/>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>153</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -3888,60 +3874,62 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">064
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="n"/>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="Q26" s="3" t="n"/>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1153
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -3958,128 +3946,133 @@
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">7155
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">379
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="n"/>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">153
 </t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>043</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2000
-</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -4096,16 +4089,21 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -4115,15 +4113,10 @@
 </t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
+      <c r="G28" s="3" t="n"/>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -4134,93 +4127,93 @@
 </t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
-      </c>
+      <c r="K28" s="3" t="n"/>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="n"/>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21610
+</t>
+        </is>
+      </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">9360
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">2411
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4240,129 +4233,135 @@
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="n"/>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>51</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">2150
+</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>4241</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">990
 </t>
         </is>
       </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t>4343</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="T29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">661
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="W29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1310
-</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -4381,14 +4380,19 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11168
-</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n"/>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -4400,19 +4404,19 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">459
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4421,92 +4425,99 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K30" s="3" t="n"/>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1998
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42138
+          <t xml:space="preserve">667
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>42501</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4524,46 +4535,46 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
-</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="n"/>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+89191911
+</t>
+        </is>
+      </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">943
+</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">624
-</t>
+          <t>624</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">769
@@ -4572,7 +4583,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -4584,51 +4595,59 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="n"/>
+          <t>99921</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">612
+</t>
+        </is>
+      </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">2272
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1081
-</t>
-        </is>
-      </c>
-      <c r="T31" s="3" t="n"/>
+          <t xml:space="preserve">959
+</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4132
+</t>
+        </is>
+      </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>415</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1635
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -4640,12 +4659,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>42221</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">81911955
+111
 </t>
         </is>
       </c>
@@ -4664,7 +4684,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0884
+          <t xml:space="preserve">3646
 </t>
         </is>
       </c>
@@ -4676,7 +4696,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144 1
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
@@ -4688,7 +4708,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -4700,20 +4720,20 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">084
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n"/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">7116
 </t>
         </is>
       </c>
@@ -4725,73 +4745,79 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809
+          <t xml:space="preserve">2007
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">4781
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">19 1 6
+</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="n"/>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70 6
+</t>
+        </is>
+      </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 84
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">951
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 13
+          <t xml:space="preserve">18 1
 </t>
         </is>
       </c>
@@ -4810,34 +4836,34 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4112
+          <t xml:space="preserve">4402
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>18133</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
@@ -4846,92 +4872,97 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J33" s="3" t="n"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>393</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="n"/>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1948
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="n"/>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4948,10 +4979,15 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -4963,14 +4999,13 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -4978,41 +5013,46 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1426
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="n"/>
+          <t xml:space="preserve">1292
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -5021,51 +5061,56 @@
           <t>212</t>
         </is>
       </c>
-      <c r="R34" s="3" t="n"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>65</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -5082,10 +5127,16 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>416</t>
+          <t xml:space="preserve">242
+</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -5096,30 +5147,30 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -5131,20 +5182,23 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="n"/>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">452
+</t>
+        </is>
+      </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">2920
 </t>
         </is>
       </c>
@@ -5156,48 +5210,43 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1769
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="n"/>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">9868
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -5209,7 +5258,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2186
+          <t xml:space="preserve">384
 </t>
         </is>
       </c>
@@ -5229,130 +5278,136 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1227
+</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1079
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">759
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">665
+</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">121
 </t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1664
-</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2920
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="T36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">881
-</t>
-        </is>
-      </c>
-      <c r="U36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="V36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="W36" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -5372,7 +5427,7 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -5384,7 +5439,8 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">422112
+214101
 </t>
         </is>
       </c>
@@ -5394,28 +5450,36 @@
 </t>
         </is>
       </c>
-      <c r="H37" s="3" t="n"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">455266
+72
+45
+61194929
+</t>
+        </is>
+      </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">525
 </t>
         </is>
       </c>
@@ -5427,13 +5491,13 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9878
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
@@ -5445,13 +5509,13 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -5462,15 +5526,22 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>38191</t>
+          <t xml:space="preserve">2191
+</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="n"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">816
@@ -5479,17 +5550,18 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>425</t>
+          <t xml:space="preserve">4225
+</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -5506,123 +5578,131 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n"/>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
           <t>44841</t>
         </is>
       </c>
-      <c r="E38" s="3" t="n"/>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="n"/>
+          <t xml:space="preserve">322
+</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>501</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6813
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">676
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">21372
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="n"/>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920
+          <t xml:space="preserve">4960
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10180
-</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="n"/>
+          <t>4012</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8792
+</t>
+        </is>
+      </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3809
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">176
 </t>
         </is>
       </c>
-      <c r="T38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">664
-</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5641,12 +5721,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>143</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -5664,38 +5744,39 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">777
+141
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -5706,53 +5787,53 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1084
+          <t xml:space="preserve">1381
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t xml:space="preserve">661
+</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>163</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
@@ -5761,15 +5842,10 @@
 </t>
         </is>
       </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">670
-</t>
-        </is>
-      </c>
+      <c r="Y39" s="3" t="n"/>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -5788,7 +5864,8 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6377
+          <t xml:space="preserve">227
+6443
 </t>
         </is>
       </c>
@@ -5799,13 +5876,13 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -5817,78 +5894,79 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="n"/>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">789
+</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -5900,13 +5978,12 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -5917,7 +5994,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5934,12 +6011,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4088
-</t>
-        </is>
-      </c>
+      <c r="C41" s="3" t="n"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
@@ -5948,7 +6020,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11597
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -5966,7 +6038,7 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>343</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -5977,75 +6049,71 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1013
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">700
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="n"/>
       <c r="N41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1726
+</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">488
+</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">120
 </t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">089
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">470
-</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
           <t>217</t>
@@ -6059,19 +6127,19 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1853
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6090,13 +6158,13 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6094
+          <t xml:space="preserve">6088
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -6113,43 +6181,40 @@
 </t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">472
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">56
+</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -6167,25 +6232,15 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">089
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="n"/>
+      <c r="S42" s="3" t="n"/>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">498
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
@@ -6197,7 +6252,7 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -6209,7 +6264,7 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -6220,7 +6275,7 @@
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
@@ -6239,144 +6294,129 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">60944
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">7064
 </t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1017
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111416 1
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1207
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7119
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="n"/>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9720
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="n"/>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">532
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -6395,7 +6435,8 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31195
+          <t xml:space="preserve">622
+2722208602828
 </t>
         </is>
       </c>
@@ -6407,25 +6448,20 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1017
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2124
+</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111416 1
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -6441,39 +6477,33 @@
 </t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
+      <c r="K44" s="3" t="n"/>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550020
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101101101
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -6485,56 +6515,34 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10110
-</t>
-        </is>
-      </c>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1501151000115
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="n"/>
+      <c r="T44" s="3" t="n"/>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119898
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">981
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">24222
+7
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="n"/>
+      <c r="X44" s="3" t="n"/>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t xml:space="preserve">422
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -6556,7 +6564,8 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">672727
+</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -6566,7 +6575,8 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">84
+24222
 </t>
         </is>
       </c>
@@ -6578,22 +6588,17 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
-</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6602,24 +6607,20 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
+          <t xml:space="preserve">6022
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="n"/>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6219
+          <t xml:space="preserve">61972
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4980
+          <t xml:space="preserve">6242
 </t>
         </is>
       </c>
@@ -6638,49 +6639,50 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">8272
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29298
+          <t xml:space="preserve">2181
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
+          <t xml:space="preserve">12089
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3288
+          <t xml:space="preserve">378
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">87
+</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6698,24 +6700,25 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>231</t>
+          <t xml:space="preserve">107
+</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -6733,50 +6736,43 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">3821
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">559
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1044
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -6787,49 +6783,39 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">505
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">831
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">881
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">929180
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="n"/>
+      <c r="X46" s="3" t="n"/>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
@@ -734,125 +734,127 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">71138
 </t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="n"/>
+          <t xml:space="preserve">2108
+</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12668
+</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>4112</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960
-</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">2930
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -870,24 +872,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4645
+          <t xml:space="preserve">15643
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t xml:space="preserve">1255
+</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -898,18 +900,18 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -921,7 +923,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
@@ -931,41 +933,39 @@
 </t>
         </is>
       </c>
-      <c r="N5" s="3" t="n"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-990
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">988
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1839
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -977,13 +977,12 @@
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -995,14 +994,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">2930
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1020,20 +1018,19 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">389
+          <t xml:space="preserve">3380
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -1044,25 +1041,30 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>01400</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="n"/>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111416
+</t>
+        </is>
+      </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1073,43 +1075,42 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">09942
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1161
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>217</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">6718
 </t>
         </is>
       </c>
@@ -1121,29 +1122,29 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>120</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9310
+          <t xml:space="preserve">1930
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">11039
 </t>
         </is>
       </c>
@@ -1162,7 +1163,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3552
+          <t xml:space="preserve">3557
 </t>
         </is>
       </c>
@@ -1174,129 +1175,112 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">2801
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>414</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>522</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1771
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
+          <t xml:space="preserve">2985
+</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="n"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">770
+</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">94
 </t>
         </is>
       </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">720
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
-</t>
-        </is>
-      </c>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="n"/>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">1840
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1315,132 +1299,132 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">3779
+</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1196
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>4412</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2121
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149712
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="n"/>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">790
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">72
 </t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127219
-</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">19178
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">1850
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
@@ -1457,71 +1441,70 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1825281
+</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1260
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>550</t>
+          <t xml:space="preserve">550
+</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1342
+          <t xml:space="preserve">1615
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t xml:space="preserve">289
+</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">799
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>451</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1534,49 +1517,51 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8929
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
+          <t xml:space="preserve">1956
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t xml:space="preserve">9988
+</t>
         </is>
       </c>
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
+          <t xml:space="preserve">2953
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">8712
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">1948
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4290
+          <t xml:space="preserve">194290
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">161
+</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1592,45 +1577,40 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3650
+</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -1643,71 +1623,53 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16379
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">430
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">986
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n"/>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">541
-</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="n"/>
+      <c r="V10" s="3" t="n"/>
+      <c r="W10" s="3" t="n"/>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1901
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -1719,7 +1681,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
@@ -1738,127 +1700,127 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77871
+          <t xml:space="preserve">3296
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2531
-228548177
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>133</t>
+          <t xml:space="preserve">1107
+</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="n"/>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="n"/>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">2016
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1426
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t xml:space="preserve">1223
+</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>18114</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">12895
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">720
+</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">74
+</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>846</t>
+          <t xml:space="preserve">1186
+</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t xml:space="preserve">1181
+</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">988
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1874,64 +1836,81 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t xml:space="preserve">5212
+</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n"/>
+          <t xml:space="preserve">2317
+</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1139
+</t>
+        </is>
+      </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>041</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277275
-163
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">2999
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1942,19 +1921,19 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">2172
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1469
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
@@ -1966,30 +1945,31 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">193
+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8850
+          <t xml:space="preserve">2840
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -2008,44 +1988,41 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">94556
+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">246
 </t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1891
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">21138
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2056,34 +2033,39 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>411</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>447</t>
+          <t xml:space="preserve">17176
+</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n"/>
+          <t xml:space="preserve">1990
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">238
@@ -2092,25 +2074,24 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>493</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -2122,25 +2103,25 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">078
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -2157,79 +2138,81 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203199
+</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3561
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>435</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9908
+          <t xml:space="preserve">18202
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9979
+          <t xml:space="preserve">9290
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -2251,44 +2234,34 @@
 </t>
         </is>
       </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+      <c r="T14" s="3" t="n"/>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1718
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2065
-</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="n"/>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
@@ -2305,7 +2278,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4845
+</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">267
@@ -2314,110 +2292,94 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1296
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11007
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3252
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="inlineStr">
         <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1016
+</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9480
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="n"/>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184883
-</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9226
-</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="n"/>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">480
-</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
+      <c r="X15" s="3" t="n"/>
       <c r="Y15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">848
@@ -2426,7 +2388,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
@@ -2445,44 +2407,43 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">23269
+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1272
 </t>
         </is>
       </c>
-      <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
+          <t xml:space="preserve">2957
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4236
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1954819
+</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -2494,82 +2455,89 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="n"/>
+          <t xml:space="preserve">1669
+</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">662
+</t>
+        </is>
+      </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">194910
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1157
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t xml:space="preserve">929
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9416
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
+          <t xml:space="preserve">3130
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>53</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1909
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t xml:space="preserve">9290
+</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">184
+</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2585,72 +2553,76 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>4145</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2579
+          <t xml:space="preserve">2592
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">653
-</t>
+          <t>430</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">11191
+</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">18241
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4891
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t xml:space="preserve">1139
+</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1132
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4381
-</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="n"/>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">237
@@ -2659,53 +2631,53 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>41</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
+          <t xml:space="preserve">5626
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t xml:space="preserve">1112
+</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2014
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1996
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">8980
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">2974
 </t>
         </is>
       </c>
@@ -2722,22 +2694,27 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3357
+</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">1143
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -2749,103 +2726,89 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="n"/>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1940
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="n"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="n"/>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">1229
+</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">27190
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">1740
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="n"/>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2102
+</t>
+        </is>
+      </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">767
+          <t xml:space="preserve">5167
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>6340880</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2863,68 +2826,74 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 85 2
+          <t xml:space="preserve">4356
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">111626
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="n"/>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
       <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
-      <c r="P19" s="3" t="n"/>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1968
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>143</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -2940,36 +2909,32 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1561
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="n"/>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>195</t>
+          <t xml:space="preserve">1199
+</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1175
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">8948
 </t>
         </is>
       </c>
@@ -2992,76 +2957,70 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4949
+</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">112494
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n"/>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="n"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -3072,48 +3031,44 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">175
+</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1167
+</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="n"/>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="n"/>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>434</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="n"/>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -3130,46 +3085,56 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3793
+</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="n"/>
+          <t xml:space="preserve">11796
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">2888
+</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -3181,24 +3146,20 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="n"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -3210,7 +3171,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3220,48 +3181,33 @@
 </t>
         </is>
       </c>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
+      <c r="T21" s="3" t="n"/>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">947
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">11694
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="n"/>
+      <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -3275,140 +3221,126 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5089
+</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>458</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">21132
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="n"/>
+          <t xml:space="preserve">1295
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2121
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="n"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1016
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="n"/>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2891
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1892
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="n"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -3424,138 +3356,137 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">20894
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">11285
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">11614
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">539
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">696
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">294890
+</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">066
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">11136
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="n"/>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1918
+</t>
+        </is>
+      </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">23280
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>492</t>
+          <t xml:space="preserve">12198
+</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
+          <t xml:space="preserve">1943
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">1863
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">939
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
+          <t xml:space="preserve">94290
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t>763</t>
+          <t xml:space="preserve">1169
+</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3573,124 +3504,110 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n"/>
+          <t xml:space="preserve">4379 18
+</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10256
+</t>
+        </is>
+      </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6215659
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1139
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="n"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="n"/>
+          <t xml:space="preserve">978
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">2399
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="n"/>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3281
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1731
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11894
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="n"/>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>9300407</t>
+          <t xml:space="preserve">188812
+</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">858
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="n"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3704,94 +3621,132 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2336
+</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122 1
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="n"/>
+          <t xml:space="preserve">1199
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28726
+</t>
+        </is>
+      </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1136
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">372
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="n"/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="n"/>
+          <t xml:space="preserve">1020
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="n"/>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1980
+</t>
+        </is>
+      </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="n"/>
-      <c r="S25" s="3" t="n"/>
+          <t xml:space="preserve">5189
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="U25" s="3" t="n"/>
-      <c r="V25" s="3" t="n"/>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4158
-41419
-</t>
-        </is>
-      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="n"/>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="Y25" s="3" t="n"/>
-      <c r="Z25" s="3" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -3805,128 +3760,136 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2583
+</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">11189
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115178685
-1149791
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>016</t>
+          <t xml:space="preserve">07
+</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="n"/>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1828
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">064
+          <t xml:space="preserve">1010
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>643</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="n"/>
+          <t xml:space="preserve">9318
+</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">0153
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
@@ -3943,136 +3906,125 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5358
+</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">12245
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155
+          <t xml:space="preserve">7133
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">11189
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">379
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">20916
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="n"/>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">11835
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="n"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n"/>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1990
+</t>
+        </is>
+      </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="n"/>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4091,129 +4043,126 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">3313
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="n"/>
+          <t xml:space="preserve">11817
+</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="n"/>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1328
+</t>
+        </is>
+      </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>445</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21610
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="n"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9360
-</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="n"/>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>422</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2411
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>412</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4230,138 +4179,129 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3091
+</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t xml:space="preserve">190
+</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n"/>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11122
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">131
+</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2150
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">9910
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1121
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="n"/>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">8561
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1858
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">119910
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4380,54 +4320,55 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">15699
+</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1168
 </t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">719
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1943
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">15449
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">16294
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">45
+</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">1769
 </t>
         </is>
       </c>
@@ -4437,87 +4378,70 @@
 </t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>4449244</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">2121
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">999
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">959
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">667
+          <t xml:space="preserve">94138
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1859
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1829
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="n"/>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">9220
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4535,137 +4459,129 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">3140
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-89191911
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>624</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">769
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">084
+</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">743
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>99921</t>
+          <t xml:space="preserve">859
+</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">024
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2272
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4132
+          <t xml:space="preserve">81154
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">1063
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">1 85
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>42221</t>
+          <t xml:space="preserve">950
+</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81911955
-111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4684,143 +4600,105 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3646
+          <t xml:space="preserve">3642
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">2579
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
-</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">128213
+</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>391</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7116
+          <t xml:space="preserve">7196
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2007
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="n"/>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4781
-</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19 1 6
-</t>
-        </is>
-      </c>
-      <c r="T32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">911
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="n"/>
+      <c r="T32" s="3" t="n"/>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70 6
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="n"/>
+      <c r="W32" s="3" t="n"/>
+      <c r="X32" s="3" t="n"/>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">951
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18 1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">960
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -4836,133 +4714,126 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4402
+          <t xml:space="preserve">4112
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">1132
+</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t xml:space="preserve">11817
+</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">11000
+</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>393</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">110972
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">998
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">201912
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="S33" s="3" t="n"/>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
+      <c r="T33" s="3" t="n"/>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">2916
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">19800
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -4981,136 +4852,121 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">946
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11452
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="n"/>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2990
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">182
 </t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>1025</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="n"/>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1426
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1292
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">778
-</t>
-        </is>
-      </c>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="n"/>
+      <c r="T34" s="3" t="n"/>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>432</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5129,136 +4985,135 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">4778
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">1121
+</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">452
+          <t xml:space="preserve">1212818
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="n"/>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9868
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="n"/>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>484</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>65</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">2840
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">384
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5275,139 +5130,133 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6132
+</t>
+        </is>
+      </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">1138
+</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
-</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">759
+          <t xml:space="preserve">11150
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="T36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">665
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11616
+</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="n"/>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>412</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1326
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5424,145 +5273,142 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>197824</t>
+        </is>
+      </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">11184
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">422112
-214101
+          <t xml:space="preserve">10922
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">523
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">455266
-72
-45
-61194929
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1501
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">16815
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1676
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">94920
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1899
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t xml:space="preserve">889
+</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2191
-</t>
+          <t>3821914</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">2332
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">1816
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">880
+</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4225
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5580,129 +5426,122 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>44841</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4956
+</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n"/>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">1741
+</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">1913
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="n"/>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21372
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="n"/>
+          <t xml:space="preserve">1174
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2190
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n"/>
+      <c r="L38" s="3" t="n"/>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4960
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">034
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>302</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8792
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">11720
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3809
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">1664
+</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
+          <t xml:space="preserve">181014
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="n"/>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">01846
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -5721,128 +5560,121 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">6243
+</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">11815
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">777
-141
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2193
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="n"/>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">121202
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1381
+          <t xml:space="preserve">2012
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1505
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">661
-</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="W39" s="3" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="n"/>
+      <c r="W39" s="3" t="n"/>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="3" t="n"/>
+          <t xml:space="preserve">1988
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1628
+</t>
+        </is>
+      </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">32
@@ -5864,25 +5696,25 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-6443
+          <t xml:space="preserve">6377
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>259</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -5892,64 +5724,64 @@
 </t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">11100
+</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">2354
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">789
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -5960,41 +5792,42 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">0488
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t xml:space="preserve">1169
+</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -6011,135 +5844,121 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n"/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7943
+</t>
+        </is>
+      </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">397
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1262
+</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1013
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11208
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="n"/>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1019
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="n"/>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">881
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">179
 </t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">700
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1726
-</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">488
-</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>217</t>
+          <t xml:space="preserve">2 1 4
+</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1853
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -6164,39 +5983,49 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n"/>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24709
+</t>
+        </is>
+      </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">11224
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="n"/>
+          <t xml:space="preserve">11605
+</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">472
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">359
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6206,24 +6035,14 @@
 </t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
+      <c r="M42" s="3" t="n"/>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">932
+</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="n"/>
       <c r="P42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">04
@@ -6232,15 +6051,25 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="n"/>
-      <c r="S42" s="3" t="n"/>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">9490
 </t>
         </is>
       </c>
@@ -6252,30 +6081,31 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">158
+</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -6294,82 +6124,74 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60944
+          <t xml:space="preserve">6044
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7064
-</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="n"/>
+          <t xml:space="preserve">1810
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7119
-</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
+      <c r="N43" s="3" t="n"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="n"/>
+          <t xml:space="preserve">1920
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="n"/>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6381,19 +6203,19 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">399
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -6404,19 +6226,19 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
+          <t xml:space="preserve">7298
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -6433,115 +6255,29 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">622
-2722208602828
-</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2124
-</t>
-        </is>
-      </c>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="3" t="n"/>
+      <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="n"/>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
+      <c r="L44" s="3" t="n"/>
+      <c r="M44" s="3" t="n"/>
+      <c r="N44" s="3" t="n"/>
+      <c r="O44" s="3" t="n"/>
+      <c r="P44" s="3" t="n"/>
+      <c r="Q44" s="3" t="n"/>
+      <c r="R44" s="3" t="n"/>
       <c r="S44" s="3" t="n"/>
       <c r="T44" s="3" t="n"/>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24222
-7
-</t>
-        </is>
-      </c>
+      <c r="U44" s="3" t="n"/>
+      <c r="V44" s="3" t="n"/>
       <c r="W44" s="3" t="n"/>
       <c r="X44" s="3" t="n"/>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
-      </c>
+      <c r="Y44" s="3" t="n"/>
       <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -6564,19 +6300,18 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">672727
-</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>534</t>
+          <t xml:space="preserve">036
+</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-24222
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -6588,100 +6323,113 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="n"/>
+          <t xml:space="preserve">11819
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6022
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="n"/>
+          <t xml:space="preserve">3564
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">559
+</t>
+        </is>
+      </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61972
+          <t xml:space="preserve">1689
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6242
-</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="n"/>
+          <t>4960</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1248
+</t>
+        </is>
+      </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">11263
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8272
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181
+          <t xml:space="preserve">12822
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12089
+          <t xml:space="preserve">11089
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
+          <t xml:space="preserve">10609
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">378
+          <t xml:space="preserve">23028 1
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6700,31 +6448,30 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2239
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">15034
 </t>
         </is>
       </c>
@@ -6736,89 +6483,81 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3821
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1595
 </t>
         </is>
       </c>
       <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t xml:space="preserve">11113
+</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">490
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="n"/>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">044
+</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">2353
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="n"/>
+      <c r="T46" s="3" t="n"/>
       <c r="U46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18654
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929180
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="3" t="n"/>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+      <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
@@ -734,13 +734,13 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
@@ -750,16 +750,21 @@
 </t>
         </is>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2108
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -771,7 +776,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
@@ -783,13 +788,13 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -801,19 +806,20 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">8202
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12668
+          <t xml:space="preserve">8197
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">1893
+</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -828,15 +834,21 @@
 </t>
         </is>
       </c>
-      <c r="U4" s="3" t="n"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
@@ -848,13 +860,14 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">109
+</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -872,19 +885,20 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15643
+          <t xml:space="preserve">1645
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1140
+</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -895,7 +909,8 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>425</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -906,24 +921,25 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -941,19 +957,25 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n"/>
+          <t xml:space="preserve">958
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>213</t>
+          <t xml:space="preserve">213
+</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -977,12 +999,13 @@
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
@@ -994,13 +1017,14 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1024,29 +1048,31 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">1049
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">19
+</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">101
+</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111416
+          <t xml:space="preserve">11106
 </t>
         </is>
       </c>
@@ -1058,30 +1084,31 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09942
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1161
+          <t xml:space="preserve">1215621
 </t>
         </is>
       </c>
@@ -1091,7 +1118,12 @@
 </t>
         </is>
       </c>
-      <c r="P6" s="3" t="n"/>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">222
@@ -1100,17 +1132,19 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6718
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
@@ -1122,29 +1156,31 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11039
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1163,7 +1199,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3557
+          <t xml:space="preserve">2552
 </t>
         </is>
       </c>
@@ -1175,7 +1211,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -1187,23 +1223,25 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2801
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -1215,12 +1253,14 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>414</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>522</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1231,11 +1271,16 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2985
-</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="n"/>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
@@ -1244,10 +1289,16 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="n"/>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">770
@@ -1262,19 +1313,25 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
-      <c r="X7" s="3" t="n"/>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -1299,7 +1356,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3779
+          <t xml:space="preserve">3778
 </t>
         </is>
       </c>
@@ -1317,47 +1374,55 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n"/>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">2141
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">1152
+</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149712
+          <t xml:space="preserve">1314
 </t>
         </is>
       </c>
@@ -1369,26 +1434,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">790
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
@@ -1400,13 +1470,13 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19178
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
@@ -1418,13 +1488,13 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1443,17 +1513,22 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825281
+          <t xml:space="preserve">18252
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n"/>
+          <t xml:space="preserve">1265
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">715
+</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">990
@@ -1462,13 +1537,13 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">050
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
+          <t xml:space="preserve">615
 </t>
         </is>
       </c>
@@ -1480,38 +1555,49 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">12819
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">749
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="n"/>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="n"/>
+          <t xml:space="preserve">4238
+</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1033
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -1523,20 +1609,25 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1956
+          <t xml:space="preserve">9856
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9988
-</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="n"/>
+          <t xml:space="preserve">09101
+</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2953
+          <t xml:space="preserve">955
 </t>
         </is>
       </c>
@@ -1548,19 +1639,19 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">9498
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194290
+          <t xml:space="preserve">942908
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -1579,7 +1670,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
+          <t xml:space="preserve">36501
 </t>
         </is>
       </c>
@@ -1591,17 +1682,28 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">412
+</t>
+        </is>
+      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">13
@@ -1610,26 +1712,31 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1580
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1639,10 +1746,15 @@
 </t>
         </is>
       </c>
-      <c r="P10" s="3" t="n"/>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83 8
+</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -1664,9 +1776,23 @@
 </t>
         </is>
       </c>
-      <c r="U10" s="3" t="n"/>
-      <c r="V10" s="3" t="n"/>
-      <c r="W10" s="3" t="n"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1174
+</t>
+        </is>
+      </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -1675,13 +1801,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1710,8 +1836,18 @@
 </t>
         </is>
       </c>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1853
+</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1139
+</t>
+        </is>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">101
@@ -1720,67 +1856,73 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">097
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n"/>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">527
+</t>
+        </is>
+      </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">1623
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>18114</t>
+          <t xml:space="preserve">187
+</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12895
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1792,13 +1934,13 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -1810,17 +1952,22 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="n"/>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1836,104 +1983,109 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5212
+          <t xml:space="preserve">5811
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2317
+          <t xml:space="preserve">2517
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2539
+</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2198
+</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0800
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">090
+</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1139
 </t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1222
-</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1249
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2999
-</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2172
-</t>
-        </is>
-      </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">141046
 </t>
         </is>
       </c>
@@ -1945,13 +2097,13 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
@@ -1963,13 +2115,13 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2840
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1988,7 +2140,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94556
+          <t xml:space="preserve">5556
 </t>
         </is>
       </c>
@@ -2000,29 +2152,32 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t xml:space="preserve">2216
+</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21138
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2039,30 +2194,31 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t xml:space="preserve">111
+</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17176
+          <t xml:space="preserve">8196
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2074,7 +2230,8 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>493</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -2085,16 +2242,11 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">668
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="n"/>
       <c r="V13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -2103,13 +2255,13 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">078
+          <t xml:space="preserve">1978
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -2121,7 +2273,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2140,7 +2292,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203199
+          <t xml:space="preserve">0318
 </t>
         </is>
       </c>
@@ -2152,67 +2304,73 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t xml:space="preserve">2045
+</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">96
+</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>435</t>
+          <t xml:space="preserve">1125
+</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18202
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9290
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2234,25 +2392,36 @@
 </t>
         </is>
       </c>
-      <c r="T14" s="3" t="n"/>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">711
+</t>
+        </is>
+      </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="n"/>
+          <t xml:space="preserve">1184
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">840
@@ -2261,7 +2430,7 @@
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -2292,47 +2461,64 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1296
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11007
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n"/>
+          <t xml:space="preserve">2120821
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="n"/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n"/>
+          <t xml:space="preserve">1199
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">970
@@ -2341,13 +2527,14 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">2257
+</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
@@ -2364,25 +2551,37 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480
-</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="n"/>
+          <t xml:space="preserve">96480
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="n"/>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">8248
 </t>
         </is>
       </c>
@@ -2407,7 +2606,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23269
+          <t xml:space="preserve">230691
 </t>
         </is>
       </c>
@@ -2419,31 +2618,37 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">643
+</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2957
+          <t xml:space="preserve">957
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1954819
-</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n"/>
+          <t xml:space="preserve">589
+</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1397
+</t>
+        </is>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -2455,36 +2660,37 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1669
+          <t xml:space="preserve">969
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>844</t>
+          <t xml:space="preserve">706
+</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194910
+          <t xml:space="preserve">4818
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
+          <t xml:space="preserve">11157
 </t>
         </is>
       </c>
@@ -2508,35 +2714,37 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">558
+</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t xml:space="preserve">11004
+</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9290
+          <t xml:space="preserve">9210
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -2555,35 +2763,38 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t xml:space="preserve">48141
+</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>430</t>
+          <t xml:space="preserve">1130
+</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11191
+          <t xml:space="preserve">1971
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18241
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -2594,10 +2805,16 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n"/>
+          <t xml:space="preserve">2164
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1139
@@ -2606,20 +2823,25 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="n"/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2631,7 +2853,8 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -2642,42 +2865,43 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5626
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8980
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2974
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
@@ -2696,13 +2920,13 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3357
+          <t xml:space="preserve">9557
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2009
 </t>
         </is>
       </c>
@@ -2714,54 +2938,79 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">8191
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="n"/>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="n"/>
+          <t xml:space="preserve">11822
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="n"/>
+          <t xml:space="preserve">9809
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -2773,42 +3022,44 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2102
+          <t xml:space="preserve">2106
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5167
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">680
+</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2826,30 +3077,31 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
+          <t xml:space="preserve">4556
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t xml:space="preserve">257
+</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111626
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">11993
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2859,29 +3111,40 @@
 </t>
         </is>
       </c>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">1642
+</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">2108
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1968
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -2893,7 +3156,8 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">243
+</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -2904,37 +3168,43 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t xml:space="preserve">1794
+</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="n"/>
+          <t xml:space="preserve">361
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1294
+</t>
+        </is>
+      </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">11995
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">1985
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
@@ -2959,56 +3229,68 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4949
-</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n"/>
+          <t xml:space="preserve">14949
+</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">022
+</t>
+        </is>
+      </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112494
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">11958
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n"/>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">3
+</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">022
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">1124
+</t>
         </is>
       </c>
       <c r="N20" s="3" t="n"/>
@@ -3020,13 +3302,14 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t xml:space="preserve">1035
+</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
@@ -3041,34 +3324,45 @@
 </t>
         </is>
       </c>
-      <c r="T20" s="3" t="n"/>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1880
+</t>
+        </is>
+      </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>434</t>
+          <t xml:space="preserve">2588
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="Y20" s="3" t="n"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">879
+</t>
+        </is>
+      </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -3087,48 +3381,49 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3793
+          <t xml:space="preserve">3713
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">2036
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">8916080
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t xml:space="preserve">1198
+</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11796
+          <t xml:space="preserve">1956
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">1895
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2888
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -3146,20 +3441,25 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="n"/>
+          <t xml:space="preserve">1163
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1887
+</t>
+        </is>
+      </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">18080
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -3177,26 +3477,31 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="n"/>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">809
+</t>
+        </is>
+      </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">947
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11694
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
@@ -3206,7 +3511,12 @@
 </t>
         </is>
       </c>
-      <c r="Y21" s="3" t="n"/>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">981
+</t>
+        </is>
+      </c>
       <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -3229,30 +3539,31 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>458</t>
+          <t xml:space="preserve">2258
+</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21132
+          <t xml:space="preserve">1131
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -3271,55 +3582,67 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="n"/>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1214
+</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="n"/>
+          <t xml:space="preserve">016
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1046
+</t>
+        </is>
+      </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">18 7
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">59
+</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3331,7 +3654,8 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>361</t>
+          <t xml:space="preserve">201
+</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -3340,7 +3664,12 @@
 </t>
         </is>
       </c>
-      <c r="Z22" s="3" t="n"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -3368,18 +3697,19 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">975
+</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11614
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -3391,13 +3721,13 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -3409,83 +3739,91 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>205</t>
+          <t xml:space="preserve">2071
+</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="n"/>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294890
+          <t xml:space="preserve">4890
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1
+</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11136
+          <t xml:space="preserve">115136
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t xml:space="preserve">915
+</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23280
+          <t xml:space="preserve">3280
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12198
+          <t xml:space="preserve">1498
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1863
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">939
+          <t xml:space="preserve">9389
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94290
+          <t xml:space="preserve">4298
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">11963
 </t>
         </is>
       </c>
@@ -3504,30 +3842,40 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4379 18
+          <t xml:space="preserve">49729
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10256
+          <t xml:space="preserve">0256
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="n"/>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6215659
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="n"/>
+          <t xml:space="preserve">1234
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1085
+</t>
+        </is>
+      </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">22
@@ -3536,14 +3884,20 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
+          <t xml:space="preserve">597
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 4
+</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -3552,7 +3906,12 @@
 </t>
         </is>
       </c>
-      <c r="N24" s="3" t="n"/>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">978
@@ -3561,24 +3920,31 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">044
+</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399
+          <t xml:space="preserve">2919
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="n"/>
+          <t xml:space="preserve">1853
+</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -3590,14 +3956,19 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11894
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="n"/>
+          <t xml:space="preserve">1894
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1731
+</t>
+        </is>
+      </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188812
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -3607,7 +3978,12 @@
 </t>
         </is>
       </c>
-      <c r="Z24" s="3" t="n"/>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3623,91 +3999,97 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2336
+          <t xml:space="preserve">2536
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">11539
+</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28726
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">121356
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">817
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">1962
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -3719,31 +4101,43 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>1114</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="n"/>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="n"/>
+          <t xml:space="preserve">1719
+</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1220
+</t>
+        </is>
+      </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3762,7 +4156,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2583
+          <t xml:space="preserve">2683
 </t>
         </is>
       </c>
@@ -3774,19 +4168,19 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -3804,44 +4198,55 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n"/>
+          <t xml:space="preserve">11158
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">888080
+</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -3853,13 +4258,13 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9318
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3871,25 +4276,25 @@
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0153
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -3908,81 +4313,98 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5358
+          <t xml:space="preserve">93517
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7133
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">013125
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20916
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="n"/>
+          <t xml:space="preserve">0116
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1117
+</t>
+        </is>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">16
 </t>
         </is>
       </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11835
+          <t xml:space="preserve">1735
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="n"/>
+          <t xml:space="preserve">2258
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1018
+</t>
+        </is>
+      </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -4005,7 +4427,7 @@
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -4015,10 +4437,15 @@
 </t>
         </is>
       </c>
-      <c r="X27" s="3" t="n"/>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -4043,7 +4470,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3313
+          <t xml:space="preserve">3318
 </t>
         </is>
       </c>
@@ -4061,7 +4488,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -4073,50 +4500,68 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="n"/>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8075
+</t>
+        </is>
+      </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">03
+</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1328
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="n"/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">980
 </t>
         </is>
       </c>
-      <c r="P28" s="3" t="n"/>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>422</t>
+          <t xml:space="preserve">1170
+</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -4127,13 +4572,13 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4145,7 +4590,8 @@
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">1170
+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
@@ -4193,66 +4639,78 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n"/>
+          <t xml:space="preserve">20185
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11122
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="n"/>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">13
+</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">1150
+</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9910
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -4262,10 +4720,15 @@
 </t>
         </is>
       </c>
-      <c r="S29" s="3" t="n"/>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8561
+          <t xml:space="preserve">661
 </t>
         </is>
       </c>
@@ -4277,31 +4740,31 @@
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1858
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119910
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1794
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -4338,19 +4801,19 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15449
+          <t xml:space="preserve">6499
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16294
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
@@ -4362,38 +4825,49 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1769
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="3" t="n"/>
+          <t xml:space="preserve">749
+</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">745
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>4449244</t>
+          <t xml:space="preserve">4910
+</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121
+          <t xml:space="preserve">4121
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">9989
 </t>
         </is>
       </c>
@@ -4405,43 +4879,50 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">954
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94138
+          <t xml:space="preserve">41351
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">857
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="n"/>
+          <t xml:space="preserve">8294
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
+</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9220
+          <t xml:space="preserve">65480
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">99
+</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4465,7 +4946,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -4483,47 +4964,56 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1125
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">084
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n"/>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1150
 </t>
         </is>
       </c>
-      <c r="M31" s="3" t="n"/>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1199
+</t>
+        </is>
+      </c>
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">14544
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">024
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -4534,45 +5024,40 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1078
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81154
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>02</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">180101
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1063
-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 85
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="n"/>
       <c r="Y31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">950
@@ -4581,7 +5066,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -4606,66 +5091,73 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2579
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t xml:space="preserve">1319
+</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128213
+          <t xml:space="preserve">1810
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="n"/>
+          <t xml:space="preserve">829
+</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>793</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7196
+          <t xml:space="preserve">2116
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">751
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="n"/>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -4681,24 +5173,54 @@
 </t>
         </is>
       </c>
-      <c r="S32" s="3" t="n"/>
-      <c r="T32" s="3" t="n"/>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="n"/>
-      <c r="W32" s="3" t="n"/>
-      <c r="X32" s="3" t="n"/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1266
+</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11817
+</t>
+        </is>
+      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="n"/>
+          <t xml:space="preserve">1960
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -4726,7 +5248,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -4738,48 +5260,55 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">110080
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="n"/>
+          <t xml:space="preserve">1115
+</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">1049
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110972
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">9628
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -4791,49 +5320,61 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201912
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="n"/>
-      <c r="T33" s="3" t="n"/>
+          <t xml:space="preserve">1864
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">718
+</t>
+        </is>
+      </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2916
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">1165
+</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19800
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4852,18 +5393,19 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t xml:space="preserve">2114
+</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">11972
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">11597
 </t>
         </is>
       </c>
@@ -4875,98 +5417,121 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11452
-</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="n"/>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">003
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t xml:space="preserve">985
+</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="n"/>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1969
+</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">981
+</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">169
 </t>
         </is>
       </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="n"/>
-      <c r="T34" s="3" t="n"/>
-      <c r="U34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="V34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1169
-</t>
-        </is>
-      </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">1866
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -4991,7 +5556,8 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -5002,7 +5568,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">21818
 </t>
         </is>
       </c>
@@ -5020,12 +5586,13 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -5043,13 +5610,13 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212818
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
@@ -5067,22 +5634,28 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>233</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="T35" s="3" t="n"/>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">688
+</t>
+        </is>
+      </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">118
@@ -5091,29 +5664,31 @@
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t>484</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2840
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -5138,42 +5713,43 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">17138
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t xml:space="preserve">10995
+</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">11059
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">935
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5185,49 +5761,61 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11150
+          <t xml:space="preserve">0120
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="n"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1164
+</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11616
-</t>
-        </is>
-      </c>
-      <c r="T36" s="3" t="n"/>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -5239,24 +5827,25 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1326
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5275,7 +5864,8 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>197824</t>
+          <t xml:space="preserve">20782
+</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5286,30 +5876,31 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10922
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">8194
 </t>
         </is>
       </c>
@@ -5321,76 +5912,79 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
+          <t xml:space="preserve">50717
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16815
+          <t xml:space="preserve">685
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1676
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94920
+          <t xml:space="preserve">4920
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t xml:space="preserve">1010
+</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1899
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>3821914</t>
+          <t xml:space="preserve">3809
+</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2332
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>209</t>
+          <t xml:space="preserve">900
+</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1816
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
@@ -5402,13 +5996,14 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">4299
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5430,81 +6025,98 @@
 </t>
         </is>
       </c>
-      <c r="D38" s="3" t="n"/>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1237
+</t>
+        </is>
+      </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1741
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">10251
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1913
+          <t xml:space="preserve">1615
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n"/>
-      <c r="L38" s="3" t="n"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1137
+</t>
+        </is>
+      </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t xml:space="preserve">1135
+</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>414</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">034
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>302</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t xml:space="preserve">11170
+</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11720
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
@@ -5516,32 +6128,37 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181014
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="n"/>
+          <t xml:space="preserve">1801
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01846
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -5560,7 +6177,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6243
+          <t xml:space="preserve">6641
 </t>
         </is>
       </c>
@@ -5572,13 +6189,13 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -5590,32 +6207,43 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="n"/>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">8 1
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2193
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="n"/>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121202
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5627,57 +6255,67 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
+          <t xml:space="preserve">012
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">1698
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1505
+          <t xml:space="preserve">15210
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="n"/>
-      <c r="W39" s="3" t="n"/>
+          <t xml:space="preserve">2128
+</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1275
+</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0625
+</t>
+        </is>
+      </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1988
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">640
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5702,13 +6340,13 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -5720,7 +6358,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -5739,13 +6377,13 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11100
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
@@ -5757,7 +6395,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -5769,30 +6407,31 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2354
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">088
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0488
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
@@ -5804,30 +6443,31 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">173
+</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -5846,7 +6486,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7943
+          <t xml:space="preserve">6943
 </t>
         </is>
       </c>
@@ -5856,109 +6496,135 @@
 </t>
         </is>
       </c>
-      <c r="E41" s="3" t="n"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1726
+</t>
+        </is>
+      </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 37
+</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">01107
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013
+          <t xml:space="preserve">1053
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11208
-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="n"/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="n"/>
+          <t xml:space="preserve">12935
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">581
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">470
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 1 4
+          <t xml:space="preserve">813
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -5977,7 +6643,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6088
+          <t xml:space="preserve">2088
 </t>
         </is>
       </c>
@@ -5989,37 +6655,37 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24709
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11224
+          <t xml:space="preserve">11817
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11605
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">538
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">359
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6031,18 +6697,28 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="n"/>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="n"/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">04
@@ -6051,7 +6727,7 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -6063,19 +6739,19 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1474
 </t>
         </is>
       </c>
@@ -6087,25 +6763,25 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -6124,65 +6800,83 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6044
+          <t xml:space="preserve">6094
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">16 279
+</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>4340</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n"/>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110219
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1521
+</t>
+        </is>
+      </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="n"/>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">248
@@ -6203,42 +6897,43 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1680
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">399
 </t>
         </is>
       </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7298
-</t>
-        </is>
-      </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">2119
 </t>
         </is>
       </c>
@@ -6255,7 +6950,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
@@ -6300,18 +7000,19 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t xml:space="preserve">1319
+</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">036
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
@@ -6329,7 +7030,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11819
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
@@ -6341,13 +7042,13 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">0800
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3564
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
@@ -6359,77 +7060,79 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
+          <t xml:space="preserve">619
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t xml:space="preserve">4900
+</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11263
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12822
+          <t xml:space="preserve">2125
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>798</t>
+          <t xml:space="preserve">798
+</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11089
+          <t xml:space="preserve">1089
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">837
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10609
+          <t xml:space="preserve">6580
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23028 1
+          <t xml:space="preserve">3828
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">2815
 </t>
         </is>
       </c>
@@ -6454,74 +7157,85 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>405</t>
+          <t xml:space="preserve">11015
+</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">11815
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15034
+          <t xml:space="preserve">12004
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1595
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111110
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11113
+          <t xml:space="preserve">112198
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">11119
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="n"/>
+          <t xml:space="preserve">1351
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9001
+</t>
+        </is>
+      </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
+          <t xml:space="preserve">0241
 </t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2353
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -6531,8 +7245,18 @@
 </t>
         </is>
       </c>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n"/>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">598
+</t>
+        </is>
+      </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">18654
@@ -6541,24 +7265,29 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2184
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1166
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">215416
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="n"/>
       <c r="X46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">692
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1814
+</t>
+        </is>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
@@ -764,7 +764,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -788,7 +788,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -800,25 +800,25 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8202
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8197
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1893
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -830,7 +830,7 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -848,7 +848,7 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -885,7 +885,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">146495
 </t>
         </is>
       </c>
@@ -897,13 +897,13 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -933,7 +933,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -957,7 +957,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -999,13 +999,13 @@
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1023,8 +1023,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1048,19 +1047,19 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1049
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -1072,7 +1071,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11106
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1090,25 +1089,25 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215621
+          <t xml:space="preserve">12561
 </t>
         </is>
       </c>
@@ -1118,12 +1117,7 @@
 </t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+      <c r="P6" s="3" t="n"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">222
@@ -1168,7 +1162,7 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -1180,7 +1174,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1199,7 +1193,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2552
+          <t xml:space="preserve">3537
 </t>
         </is>
       </c>
@@ -1217,7 +1211,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -1253,7 +1247,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -1271,7 +1265,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1295,19 +1289,19 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1356,7 +1350,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3778
+          <t xml:space="preserve">3779
 </t>
         </is>
       </c>
@@ -1368,13 +1362,13 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
@@ -1398,7 +1392,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2141
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -1410,31 +1404,31 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">1131
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1314
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -1470,13 +1464,13 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -1525,7 +1519,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">715
+          <t xml:space="preserve">713
 </t>
         </is>
       </c>
@@ -1537,7 +1531,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">050
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
@@ -1553,15 +1547,10 @@
 </t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12819
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -1573,31 +1562,31 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">849
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4238
+          <t xml:space="preserve">4220
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1033
 </t>
         </is>
       </c>
@@ -1609,13 +1598,13 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9856
+          <t xml:space="preserve">92856
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09101
+          <t xml:space="preserve">8911
 </t>
         </is>
       </c>
@@ -1639,19 +1628,19 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9498
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942908
+          <t xml:space="preserve">94298
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
@@ -1682,7 +1671,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -1694,13 +1683,13 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -1712,31 +1701,31 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1580
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1748,7 +1737,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83 8
+          <t xml:space="preserve">6 2
 </t>
         </is>
       </c>
@@ -1772,24 +1761,25 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">191
 </t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -1832,19 +1822,19 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1853
+          <t xml:space="preserve">1333
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -1874,25 +1864,25 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">527
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">2 316
 </t>
         </is>
       </c>
@@ -1904,13 +1894,13 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1623
+          <t xml:space="preserve">1023
 </t>
         </is>
       </c>
@@ -1922,7 +1912,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2899
 </t>
         </is>
       </c>
@@ -1934,31 +1924,31 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">11886
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">2184
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -1983,7 +1973,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5811
+          <t xml:space="preserve">5011
 </t>
         </is>
       </c>
@@ -1995,7 +1985,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -2007,13 +1997,13 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0800
+          <t xml:space="preserve">01100
 </t>
         </is>
       </c>
@@ -2023,12 +2013,7 @@
 </t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1121
-</t>
-        </is>
-      </c>
+      <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">02
@@ -2037,7 +2022,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
@@ -2049,19 +2034,19 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">090
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2073,19 +2058,19 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141046
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -2121,7 +2106,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -2140,7 +2125,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5556
+          <t xml:space="preserve">1556
 </t>
         </is>
       </c>
@@ -2152,19 +2137,19 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
@@ -2194,19 +2179,19 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8196
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -2218,7 +2203,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2236,7 +2221,7 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
@@ -2246,7 +2231,12 @@
 </t>
         </is>
       </c>
-      <c r="U13" s="3" t="n"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -2255,7 +2245,7 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1978
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -2273,7 +2263,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2292,13 +2282,13 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0318
+          <t xml:space="preserve">0329
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -2316,7 +2306,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2045
+          <t xml:space="preserve">0145
 </t>
         </is>
       </c>
@@ -2334,13 +2324,13 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -2358,7 +2348,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
+          <t xml:space="preserve">1943
 </t>
         </is>
       </c>
@@ -2394,13 +2384,13 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">711
+          <t xml:space="preserve">1711
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -2412,13 +2402,13 @@
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -2449,7 +2439,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4845
+          <t xml:space="preserve">4545
 </t>
         </is>
       </c>
@@ -2461,61 +2451,61 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1149
 </t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2120821
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1199
-</t>
-        </is>
-      </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2533,7 +2523,7 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2257
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -2551,13 +2541,13 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96480
+          <t xml:space="preserve">2480
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -2569,19 +2559,19 @@
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8248
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -2606,7 +2596,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230691
+          <t xml:space="preserve">23069
 </t>
         </is>
       </c>
@@ -2618,7 +2608,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">643
+          <t xml:space="preserve">6553
 </t>
         </is>
       </c>
@@ -2636,37 +2626,37 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">589
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">1349
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">669
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -2678,19 +2668,19 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4818
+          <t xml:space="preserve">4930
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11157
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
@@ -2720,7 +2710,7 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11004
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
@@ -2732,13 +2722,13 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9210
+          <t xml:space="preserve">94210
 </t>
         </is>
       </c>
@@ -2763,13 +2753,13 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48141
+          <t xml:space="preserve">08141
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -2781,13 +2771,13 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1971
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
@@ -2805,19 +2795,18 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -2829,13 +2818,13 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -2859,7 +2848,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -2901,7 +2890,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -2926,7 +2915,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -2938,37 +2927,32 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8191
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2980,31 +2964,31 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11822
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9809
+          <t xml:space="preserve">9828
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">12168
 </t>
         </is>
       </c>
@@ -3022,31 +3006,31 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2106
+          <t xml:space="preserve">2102
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">16 7
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -3058,7 +3042,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -3077,7 +3061,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4556
+          <t xml:space="preserve">4356
 </t>
         </is>
       </c>
@@ -3089,13 +3073,13 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1630
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11993
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
@@ -3119,7 +3103,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3131,20 +3115,25 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2108
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
@@ -3156,7 +3145,7 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -3168,7 +3157,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1794
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -3180,25 +3169,25 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11995
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1985
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">2889
 </t>
         </is>
       </c>
@@ -3229,25 +3218,25 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14949
+          <t xml:space="preserve">14979
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11958
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -3265,31 +3254,31 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -3302,13 +3291,13 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1035
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -3320,13 +3309,13 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1880
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3338,13 +3327,13 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">1912
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2588
+          <t xml:space="preserve">1177
 </t>
         </is>
       </c>
@@ -3356,7 +3345,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -3387,13 +3376,13 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8916080
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
@@ -3405,19 +3394,19 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1956
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1895
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -3441,7 +3430,7 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">2163
 </t>
         </is>
       </c>
@@ -3453,7 +3442,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18080
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
@@ -3477,7 +3466,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -3489,7 +3478,7 @@
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -3501,19 +3490,19 @@
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -3539,26 +3528,25 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3573,7 +3561,12 @@
 </t>
         </is>
       </c>
-      <c r="J22" s="3" t="n"/>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">517
@@ -3582,19 +3575,19 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">11209
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3606,19 +3599,19 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1046
+          <t xml:space="preserve">12246
 </t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 7
+          <t xml:space="preserve">18 54
 </t>
         </is>
       </c>
@@ -3630,13 +3623,13 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3654,7 +3647,7 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -3691,7 +3684,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11285
+          <t xml:space="preserve">11284
 </t>
         </is>
       </c>
@@ -3709,7 +3702,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
@@ -3739,19 +3732,19 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2071
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">696
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">718
 </t>
         </is>
       </c>
@@ -3761,39 +3754,28 @@
 </t>
         </is>
       </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="P23" s="3" t="n"/>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115136
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9185
+</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3280
-</t>
+          <t>32606</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1498
+          <t xml:space="preserve">0498
 </t>
         </is>
       </c>
@@ -3805,13 +3787,13 @@
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9389
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
@@ -3823,7 +3805,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11963
+          <t xml:space="preserve">1983
 </t>
         </is>
       </c>
@@ -3842,13 +3824,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49729
+          <t xml:space="preserve">49129
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0256
+          <t xml:space="preserve">2356
 </t>
         </is>
       </c>
@@ -3872,7 +3854,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1085
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -3884,19 +3866,14 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">597
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 4
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">371
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3908,7 +3885,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3920,19 +3897,19 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
+          <t xml:space="preserve">0944
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2919
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1853
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3944,7 +3921,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">656
 </t>
         </is>
       </c>
@@ -3962,7 +3939,7 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1731
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -3980,7 +3957,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -3999,19 +3976,19 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2536
+          <t xml:space="preserve">2236
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">23 1
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11539
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4023,19 +4000,18 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121356
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -4047,13 +4023,13 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -4065,49 +4041,49 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -4119,7 +4095,7 @@
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -4131,13 +4107,13 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">9208
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -4174,40 +4150,35 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">177
 </t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -4216,7 +4187,7 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11158
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -4228,19 +4199,19 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888080
+          <t xml:space="preserve">9088
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -4258,7 +4229,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -4276,19 +4247,19 @@
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
+          <t xml:space="preserve">070
 </t>
         </is>
       </c>
@@ -4313,7 +4284,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93517
+          <t xml:space="preserve">4358
 </t>
         </is>
       </c>
@@ -4337,19 +4308,19 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">013125
+          <t xml:space="preserve">01312
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -4367,19 +4338,19 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1735
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1018
+          <t xml:space="preserve">1088
 </t>
         </is>
       </c>
@@ -4391,13 +4362,13 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -4413,12 +4384,7 @@
 </t>
         </is>
       </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
+      <c r="T27" s="3" t="n"/>
       <c r="U27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">30
@@ -4427,7 +4393,7 @@
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -4445,7 +4411,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -4470,7 +4436,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3318
+          <t xml:space="preserve">3313
 </t>
         </is>
       </c>
@@ -4488,25 +4454,25 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8075
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -4530,7 +4496,7 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -4572,13 +4538,13 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -4633,28 +4599,23 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20185
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n"/>
       <c r="H29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">122
@@ -4681,7 +4642,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>37</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4710,7 +4671,7 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -4746,13 +4707,13 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1794
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4764,7 +4725,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4807,7 +4768,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6499
+          <t xml:space="preserve">6459
 </t>
         </is>
       </c>
@@ -4825,7 +4786,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -4837,37 +4798,32 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
+          <t xml:space="preserve">799
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">690
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4910
-</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4121
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4918
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="n"/>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9989
+          <t xml:space="preserve">999
 </t>
         </is>
       </c>
@@ -4879,13 +4835,13 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
+          <t xml:space="preserve">959
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41351
+          <t xml:space="preserve">4131
 </t>
         </is>
       </c>
@@ -4897,31 +4853,31 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">857
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8294
+          <t xml:space="preserve">8249
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65480
+          <t xml:space="preserve">942280
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -4952,7 +4908,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -4970,25 +4926,25 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
+          <t xml:space="preserve">0815
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5007,15 +4963,11 @@
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14544
-</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16441
+</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">199
@@ -5024,7 +4976,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1078
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -5036,24 +4988,25 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">92116
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t xml:space="preserve">044
+</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180101
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -5066,7 +5019,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5091,13 +5044,13 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
@@ -5115,7 +5068,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
@@ -5127,34 +5080,39 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>291</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2116
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">751
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="n"/>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">82
@@ -5169,13 +5127,13 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -5187,13 +5145,13 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
@@ -5205,19 +5163,19 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5248,7 +5206,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
@@ -5260,13 +5218,13 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110080
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">2115
 </t>
         </is>
       </c>
@@ -5290,19 +5248,19 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1049
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9628
+          <t xml:space="preserve">1601
 </t>
         </is>
       </c>
@@ -5320,61 +5278,61 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">0165
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5399,13 +5357,13 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11972
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11597
+          <t xml:space="preserve">15719
 </t>
         </is>
       </c>
@@ -5417,7 +5375,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -5435,37 +5393,32 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">003
+          <t xml:space="preserve">023
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="n"/>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -5477,7 +5430,7 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1969
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -5495,7 +5448,7 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
@@ -5507,7 +5460,7 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
@@ -5519,13 +5472,13 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
@@ -5550,13 +5503,13 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -5568,13 +5521,13 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21818
+          <t xml:space="preserve">2181
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -5592,7 +5545,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -5614,12 +5567,7 @@
 </t>
         </is>
       </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1141
-</t>
-        </is>
-      </c>
+      <c r="N35" s="3" t="n"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">980
@@ -5628,25 +5576,25 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
@@ -5664,7 +5612,7 @@
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -5676,7 +5624,7 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -5713,19 +5661,19 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10995
+          <t xml:space="preserve">0195
 </t>
         </is>
       </c>
@@ -5737,13 +5685,13 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11059
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -5761,7 +5709,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0120
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -5773,25 +5721,25 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">8708
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -5809,19 +5757,19 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -5833,13 +5781,13 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -5900,7 +5848,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8194
+          <t xml:space="preserve">1814
 </t>
         </is>
       </c>
@@ -5912,7 +5860,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50717
+          <t xml:space="preserve">507
 </t>
         </is>
       </c>
@@ -5924,13 +5872,13 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">676
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5942,7 +5890,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -5960,19 +5908,19 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3809
+          <t xml:space="preserve">38019
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
@@ -5996,13 +5944,13 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4299
+          <t xml:space="preserve">4222
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6021,14 +5969,13 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4956
+          <t xml:space="preserve">4156
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
-</t>
+          <t>837</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -6039,25 +5986,25 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10251
+          <t xml:space="preserve">10351
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
+          <t xml:space="preserve">1665
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">11702
 </t>
         </is>
       </c>
@@ -6069,7 +6016,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -6092,13 +6039,13 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">984
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">02 4
 </t>
         </is>
       </c>
@@ -6110,13 +6057,13 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
@@ -6128,13 +6075,13 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1 6 1
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -6152,13 +6099,13 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -6177,7 +6124,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6641
+          <t xml:space="preserve">6244
 </t>
         </is>
       </c>
@@ -6189,7 +6136,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
@@ -6225,13 +6172,12 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 1
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6243,14 +6189,13 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -6261,7 +6206,7 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1698
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -6273,25 +6218,25 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15210
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -6303,13 +6248,13 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
@@ -6362,7 +6307,11 @@
 </t>
         </is>
       </c>
-      <c r="H40" s="3" t="n"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">38
@@ -6383,13 +6332,13 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -6407,13 +6356,13 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -6425,7 +6374,7 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -6443,7 +6392,7 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -6467,7 +6416,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6486,25 +6435,25 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6943
+          <t xml:space="preserve">6993
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1726
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
@@ -6514,12 +6463,7 @@
 </t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 37
-</t>
-        </is>
-      </c>
+      <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">47
@@ -6528,7 +6472,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6540,19 +6484,19 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01107
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1053
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6570,61 +6514,61 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12935
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1722
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">581
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
+          <t xml:space="preserve">26417
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6643,7 +6587,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088
+          <t xml:space="preserve">6088
 </t>
         </is>
       </c>
@@ -6655,7 +6599,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -6667,25 +6611,25 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">538
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -6697,25 +6641,25 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">046
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -6727,7 +6671,7 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">2617
 </t>
         </is>
       </c>
@@ -6751,7 +6695,7 @@
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -6769,19 +6713,19 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -6800,7 +6744,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6094
+          <t xml:space="preserve">50494
 </t>
         </is>
       </c>
@@ -6819,7 +6763,7 @@
       <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 279
+          <t xml:space="preserve">1 279
 </t>
         </is>
       </c>
@@ -6855,25 +6799,25 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110219
+          <t xml:space="preserve">11227
 </t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1521
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">9720
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -6897,13 +6841,13 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6915,25 +6859,25 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1680
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">399
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
+          <t xml:space="preserve">2109
 </t>
         </is>
       </c>
@@ -7006,13 +6950,13 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">536
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -7036,19 +6980,19 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0800
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
@@ -7066,13 +7010,13 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4900
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -7090,20 +7034,19 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
+          <t xml:space="preserve">21725
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
@@ -7114,25 +7057,25 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">837
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580
+          <t xml:space="preserve">681
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3828
+          <t xml:space="preserve">3028
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2815
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -7163,25 +7106,25 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11015
+          <t xml:space="preserve">11014
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12004
+          <t xml:space="preserve">810154
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -7199,31 +7142,31 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111110
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112198
+          <t xml:space="preserve">112138
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11119
+          <t xml:space="preserve">11019
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1351
+          <t xml:space="preserve">1321
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9001
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -7241,7 +7184,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
@@ -7259,13 +7202,13 @@
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18654
+          <t xml:space="preserve">13654
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215416
+          <t xml:space="preserve">218416
 </t>
         </is>
       </c>
@@ -7278,13 +7221,13 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
@@ -728,127 +728,127 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2891
+          <t xml:space="preserve">3012
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1817
 </t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">9280
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">4625
 </t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -860,13 +860,13 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">738
 </t>
         </is>
       </c>
@@ -885,145 +885,141 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146495
+          <t xml:space="preserve">3824
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1594
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">181494
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="n"/>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">805
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">4695
+</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1041,140 +1037,145 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3380
+          <t xml:space="preserve">3091
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1894
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1011
+</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1154
+</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">116
 </t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12561
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="n"/>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">029
 </t>
         </is>
       </c>
@@ -1193,145 +1194,145 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3537
+          <t xml:space="preserve">2758
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">112
 </t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1137
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">050
+</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">988
+</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0177
+</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">48
 </t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -1350,145 +1351,144 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3779
+          <t xml:space="preserve">3912
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">2673
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">227194
 </t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">760
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -1507,140 +1507,143 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18252
-</t>
+          <t>439274</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">713
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">919
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">739
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">615
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="n"/>
+          <t xml:space="preserve">979
+</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">552
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
+          <t xml:space="preserve">551
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220
+          <t xml:space="preserve">6848
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1033
+          <t xml:space="preserve">1015
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92856
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8911
+          <t xml:space="preserve">38015
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8712
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94298
+          <t xml:space="preserve">94145
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1659,145 +1662,140 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36501
+          <t xml:space="preserve">3499
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">24181
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">2130
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 2
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1177
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">7 24
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1816,145 +1814,145 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3296
+          <t xml:space="preserve">5093
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1333
+          <t xml:space="preserve">10479
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">2110
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">097
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">174
 </t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 316
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2899
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">5120
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11886
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2184
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -1973,140 +1971,145 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5011
+          <t xml:space="preserve">5061
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517
+          <t xml:space="preserve">2059
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01100
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="n"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">11917
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">8221
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">370
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">520
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -2125,145 +2128,145 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556
+          <t xml:space="preserve">3579
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">1236
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1809
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">17915
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -2282,145 +2285,140 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0329
+          <t xml:space="preserve">2270
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0145
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">2158
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1830
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1469
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1711
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="n"/>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">1595
 </t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">087
 </t>
         </is>
       </c>
@@ -2439,97 +2437,97 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4545
+          <t xml:space="preserve">6310
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">02
 </t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1726
 </t>
         </is>
       </c>
@@ -2541,43 +2539,43 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2480
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">670
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -2596,145 +2594,144 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23069
+          <t xml:space="preserve">22271
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6553
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">712
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
+          <t xml:space="preserve">395
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1349
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">669
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">582
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">706
-</t>
+          <t>571</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4930
+          <t xml:space="preserve">3990
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">11110
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">787
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
+          <t xml:space="preserve">3109
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">609
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">8017
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94210
+          <t xml:space="preserve">3690
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">339
 </t>
         </is>
       </c>
@@ -2753,144 +2750,139 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08141
+          <t xml:space="preserve">4459
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">1994
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">98718
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">0 8
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1155
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>420</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -2909,140 +2901,145 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9557
+          <t xml:space="preserve">4555
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116666
+</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">816
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21104
+</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">96
 </t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1126
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1180
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9828
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12168
-</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1190
-</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2102
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 7
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
@@ -3061,145 +3058,145 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
+          <t xml:space="preserve">5319
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1630
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">21112
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">13 0
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">0094
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">1072
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2889
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -3218,140 +3215,145 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14979
+          <t xml:space="preserve">5422
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">805
+</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1335
+</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22110
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1980
+</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">405
+</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">222
 </t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1198
-</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="n"/>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1239
-</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="U20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1912
-</t>
-        </is>
-      </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
+          <t xml:space="preserve">1894
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">12997
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3370,143 +3372,148 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3713
+          <t xml:space="preserve">3824
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">0159
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="n"/>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -3522,66 +3529,67 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089
+          <t xml:space="preserve">94890
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">139
+</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11209
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3593,73 +3601,73 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12246
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 54
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1497
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">538
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">505
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1397
 </t>
         </is>
       </c>
@@ -3678,134 +3686,144 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20894
+          <t xml:space="preserve">123203
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11284
+          <t xml:space="preserve">1321
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">2611
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">944
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">754
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
+          <t xml:space="preserve">406
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">715
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="n"/>
+          <t xml:space="preserve">2930
+</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9185
-</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="n"/>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">781
+</t>
+        </is>
+      </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>32606</t>
+          <t xml:space="preserve">2357
+</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0498
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
+          <t xml:space="preserve">1067
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
+          <t xml:space="preserve">3415
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1983
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -3824,140 +3842,139 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49129
+          <t xml:space="preserve">24641
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">1571
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">371
+          <t xml:space="preserve">7161
 </t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0944
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">11771
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">683
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -3976,144 +3993,145 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236
+          <t xml:space="preserve">14889
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 1
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">136
+</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">497
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">2415
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1376
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">01132
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1719
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">82169
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9208
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -4132,140 +4150,145 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2683
+          <t xml:space="preserve">3499
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="n"/>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">51094
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1158
 </t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9088
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">635
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">070
+          <t xml:space="preserve">1550
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
@@ -4284,140 +4307,144 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4358
+          <t xml:space="preserve">3402
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1171
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01312
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">094
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116182
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1185
+</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1135
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1088
-</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1198
-</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="n"/>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4436,145 +4463,145 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3313
+          <t xml:space="preserve">5133
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">11565
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19354
+</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1133
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">680
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28170
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1910
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1170
-</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1170
-</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4593,139 +4620,145 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091
+          <t xml:space="preserve">3233
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n"/>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1960
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1270
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11817
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">478
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">13
 </t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1150
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1190
-</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="T29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">661
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="W29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">600
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
@@ -4744,140 +4777,140 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15699
+          <t xml:space="preserve">22848
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1312
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">527
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6459
+          <t xml:space="preserve">791
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">690
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">567
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4918
-</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="n"/>
+          <t xml:space="preserve">4890
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">867
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4131
+          <t xml:space="preserve">3148
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">559
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">995
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8249
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942280
+          <t xml:space="preserve">3650
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">350
 </t>
         </is>
       </c>
@@ -4896,130 +4929,140 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140
+          <t xml:space="preserve">4320
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">26 2
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">1584
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">721
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0815
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">391
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">978
+</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7193
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1169
+</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111 1
+</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1199
 </t>
         </is>
       </c>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16441
-</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="n"/>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92116
-</t>
-        </is>
-      </c>
-      <c r="U31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">044
-</t>
-        </is>
-      </c>
-      <c r="V31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1080
-</t>
-        </is>
-      </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="n"/>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
@@ -5038,144 +5081,145 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3642
+          <t xml:space="preserve">52808
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>291</t>
+          <t xml:space="preserve">80
+</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">2201
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">2179
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">1700
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5194,145 +5238,145 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4112
+          <t xml:space="preserve">3491
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">11114
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1601
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0165
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5351,140 +5395,144 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114
+          <t xml:space="preserve">3299
 </t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15719
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">1497
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">715
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">023
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="n"/>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1159
+</t>
+        </is>
+      </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">9910
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -5503,61 +5551,61 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">5067
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
@@ -5567,76 +5615,81 @@
 </t>
         </is>
       </c>
-      <c r="N35" s="3" t="n"/>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">520
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">8168
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">6835
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -5655,49 +5708,49 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6132
+          <t xml:space="preserve">5355
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">11054
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0195
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
@@ -5709,94 +5762,88 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8708
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">050
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>446</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="Z36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">59
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="n"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -5812,73 +5859,72 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20782
-</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11184
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">609
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">6726
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">460
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
+          <t xml:space="preserve">1417
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">507
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">685
+          <t xml:space="preserve">650
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">676
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">742
 </t>
         </is>
       </c>
@@ -5890,67 +5936,66 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">1859
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38019
+          <t xml:space="preserve">2169
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">8371
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4222
+          <t xml:space="preserve">3595
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">394
 </t>
         </is>
       </c>
@@ -5969,72 +6014,69 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4156
+          <t xml:space="preserve">4481
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>837</t>
+          <t xml:space="preserve">257
+</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10351
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11702
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">901
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>414</t>
+          <t xml:space="preserve">148
+</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -6045,67 +6087,67 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02 4
+          <t xml:space="preserve">3 8
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11276
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1199
+</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">202
 </t>
         </is>
       </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1176
-</t>
-        </is>
-      </c>
-      <c r="T38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 6 1
-</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1180
-</t>
-        </is>
-      </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">719
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -6124,143 +6166,139 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6244
+          <t xml:space="preserve">5799
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">2110
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">76
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">051
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1127
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1025
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>910</t>
+          <t xml:space="preserve">980
+</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">012
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0625
+          <t xml:space="preserve">8157
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1123
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">760
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -6279,25 +6317,25 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6377
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -6309,21 +6347,17 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">83
+</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6332,91 +6366,91 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
+          <t xml:space="preserve">695
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">11815
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -6435,44 +6469,39 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6993
+          <t xml:space="preserve">4512
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -6484,20 +6513,19 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">8 6
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -6514,61 +6542,61 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1722
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">4235
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26417
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">0198
 </t>
         </is>
       </c>
@@ -6587,49 +6615,49 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6088
+          <t xml:space="preserve">5294
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">113517
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6641,94 +6669,84 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">046
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1876
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">2127
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">435
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">610
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="n"/>
+      <c r="Z42" s="3" t="n"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -6744,143 +6762,33 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50494
-</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1124
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n"/>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 279
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1130
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11227
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9720
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">398
-</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2109
-</t>
-        </is>
-      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="n"/>
+      <c r="L43" s="3" t="n"/>
+      <c r="M43" s="3" t="n"/>
+      <c r="N43" s="3" t="n"/>
+      <c r="O43" s="3" t="n"/>
+      <c r="P43" s="3" t="n"/>
+      <c r="Q43" s="3" t="n"/>
+      <c r="R43" s="3" t="n"/>
+      <c r="S43" s="3" t="n"/>
+      <c r="T43" s="3" t="n"/>
+      <c r="U43" s="3" t="n"/>
+      <c r="V43" s="3" t="n"/>
+      <c r="W43" s="3" t="n"/>
+      <c r="X43" s="3" t="n"/>
+      <c r="Y43" s="3" t="n"/>
+      <c r="Z43" s="3" t="n"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -6938,144 +6846,145 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31195
+          <t xml:space="preserve">19112
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
+          <t xml:space="preserve">10917
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">536
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">756
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">775
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
+          <t xml:space="preserve">440
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">3880
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21725
+          <t xml:space="preserve">2169
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">590
+</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
+          <t xml:space="preserve">8319
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">675
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">681
+          <t xml:space="preserve">2008
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3028
+          <t xml:space="preserve">12630
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">23318
 </t>
         </is>
       </c>
@@ -7094,140 +7003,135 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239
+          <t xml:space="preserve">4178
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11014
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810154
+          <t xml:space="preserve">1694
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
+          <t xml:space="preserve">621
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n"/>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1111819
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1970
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">064
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 47
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1886
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">116
 </t>
         </is>
       </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112138
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11019
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1321
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0241
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13654
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">541
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="n"/>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218416
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="n"/>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">18624
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
@@ -728,127 +728,127 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3012
+          <t xml:space="preserve">2891
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1197
+</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">97
 </t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1119
-</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9280
-</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1141
-</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4625
-</t>
-        </is>
-      </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -860,13 +860,13 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -885,141 +885,145 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3824
+          <t xml:space="preserve">146495
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1594
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181494
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="n"/>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4695
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1037,43 +1041,43 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091
+          <t xml:space="preserve">3380
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -1085,97 +1089,92 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1011
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">12561
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1194,145 +1193,145 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2758
+          <t xml:space="preserve">3537
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">050
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0177
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1351,144 +1350,145 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3912
+          <t xml:space="preserve">3779
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2673
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1131
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">730
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">72
 </t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227194
-</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">760
-</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1507,143 +1507,140 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>439274</t>
+          <t xml:space="preserve">18252
+</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">713
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">550
 </t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">919
-</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">739
-</t>
-        </is>
-      </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">615
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
-</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>567</t>
+          <t xml:space="preserve">749
+</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">552
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">551
+          <t xml:space="preserve">849
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6848
+          <t xml:space="preserve">4220
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1015
+          <t xml:space="preserve">1033
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">92856
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38015
+          <t xml:space="preserve">8911
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">955
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">8712
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94145
+          <t xml:space="preserve">94298
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
@@ -1662,140 +1659,145 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3499
+          <t xml:space="preserve">36501
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">986
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 2
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">20
 </t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24181
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1113
-</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1110
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2130
-</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">968
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7 24
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="W10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1170
-</t>
-        </is>
-      </c>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1814,145 +1816,145 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5093
+          <t xml:space="preserve">3296
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10479
+          <t xml:space="preserve">1333
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">097
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 316
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">02
 </t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">1023
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">2899
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5120
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">11886
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">2184
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -1971,145 +1973,140 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5061
+          <t xml:space="preserve">5011
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2059
+          <t xml:space="preserve">2517
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">2198
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">01100
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11917
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8221
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">370
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">213
 </t>
         </is>
       </c>
-      <c r="W12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -2128,145 +2125,145 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3579
+          <t xml:space="preserve">1556
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">730
+</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1112
 </t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75
-</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17915
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2285,140 +2282,145 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2270
+          <t xml:space="preserve">0329
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">0145
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2158
+          <t xml:space="preserve">1125
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1943
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="n"/>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1711
+</t>
+        </is>
+      </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1595
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">087
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -2437,97 +2439,97 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310
+          <t xml:space="preserve">4545
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1726
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -2539,43 +2541,43 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">2480
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
@@ -2594,144 +2596,145 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22271
+          <t xml:space="preserve">23069
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">6553
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">957
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">395
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1349
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">669
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>571</t>
+          <t xml:space="preserve">706
+</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3990
+          <t xml:space="preserve">4930
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11110
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3109
+          <t xml:space="preserve">3130
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">609
+          <t xml:space="preserve">558
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8017
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3690
+          <t xml:space="preserve">94210
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">339
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -2750,139 +2753,144 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4459
+          <t xml:space="preserve">08141
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1994
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98718
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n"/>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1136
-</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 8
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1169
-</t>
-        </is>
-      </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>420</t>
+          <t xml:space="preserve">626
+</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -2901,145 +2909,140 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4555
+          <t xml:space="preserve">9557
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">1143
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">67
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116666
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">9828
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">12168
 </t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21104
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">2102
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">16 7
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">680
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -3058,145 +3061,145 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319
+          <t xml:space="preserve">4356
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1630
+</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">106
 </t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21112
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 0
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0094
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">361
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">2889
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -3215,145 +3218,140 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5422
+          <t xml:space="preserve">14979
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22110
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="n"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">405
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1912
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">1177
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12997
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -3372,148 +3370,143 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3824
+          <t xml:space="preserve">3713
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">2163
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0159
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">809
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -3529,67 +3522,66 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94890
+          <t xml:space="preserve">5089
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">11209
 </t>
         </is>
       </c>
@@ -3601,73 +3593,73 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">12246
 </t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">18 54
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1497
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">538
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">505
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3686,144 +3678,134 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123203
+          <t xml:space="preserve">20894
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321
+          <t xml:space="preserve">11284
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2611
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">406
+          <t xml:space="preserve">539
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">696
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">715
+          <t xml:space="preserve">718
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4890
+</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="n"/>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">781
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9185
+</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2357
-</t>
+          <t>32606</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">0498
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1067
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3415
+          <t xml:space="preserve">4298
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
+          <t xml:space="preserve">1983
 </t>
         </is>
       </c>
@@ -3842,139 +3824,140 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24641
+          <t xml:space="preserve">49129
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">2356
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1571
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7161
+          <t xml:space="preserve">371
 </t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">0944
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">656
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11771
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">1894
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -3993,145 +3976,144 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14889
+          <t xml:space="preserve">2236
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">23 1
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">497
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2415
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1376
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01132
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">1719
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82169
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">9208
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -4150,145 +4132,140 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3499
+          <t xml:space="preserve">2683
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51094
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">9088
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">635
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1550
+          <t xml:space="preserve">070
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4307,144 +4284,140 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402
+          <t xml:space="preserve">4358
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">01312
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1088
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="n"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">880
 </t>
         </is>
       </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">094
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116182
-</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1185
-</t>
-        </is>
-      </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4463,145 +4436,145 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5133
+          <t xml:space="preserve">3313
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11565
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">87
 </t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19354
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28170
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4620,145 +4593,139 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233
+          <t xml:space="preserve">3091
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1181
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n"/>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">661
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1270
-</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11817
-</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1120
-</t>
-        </is>
-      </c>
-      <c r="T29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">478
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="V29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="W29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">600
-</t>
-        </is>
-      </c>
-      <c r="Z29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
@@ -4777,140 +4744,140 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22848
+          <t xml:space="preserve">15699
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1312
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">527
+          <t xml:space="preserve">719
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">791
+          <t xml:space="preserve">6459
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">799
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="n"/>
+          <t xml:space="preserve">743
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">690
+</t>
+        </is>
+      </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
-</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4918
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="n"/>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">999
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">959
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3148
+          <t xml:space="preserve">4131
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">995
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">8249
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
+          <t xml:space="preserve">942280
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -4929,140 +4896,130 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320
+          <t xml:space="preserve">3140
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26 2
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1584
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">721
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">0815
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n"/>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1199
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16441
+</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7193
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">92116
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111 1
+          <t xml:space="preserve">044
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1166
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="n"/>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5081,145 +5038,144 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52808
+          <t xml:space="preserve">3642
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1810
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1116
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">80
 </t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1105
-</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2201
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1121
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1182
-</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="T32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1700
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5238,145 +5194,145 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3491
+          <t xml:space="preserve">4112
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">11817
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11114
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">2115
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1601
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1194
-</t>
-        </is>
-      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">0165
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5395,144 +5351,140 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3299
+          <t xml:space="preserve">2114
 </t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">15719
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1497
+          <t xml:space="preserve">1142
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">715
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">023
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="n"/>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">17
 </t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1120
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1159
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9910
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1187
-</t>
-        </is>
-      </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">1169
+</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -5551,61 +5503,61 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5067
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">2181
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5615,81 +5567,76 @@
 </t>
         </is>
       </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
+      <c r="N35" s="3" t="n"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">688
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8168
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6835
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -5708,49 +5655,49 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5355
+          <t xml:space="preserve">6132
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11054
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">0195
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5762,88 +5709,94 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">8708
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">050
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>446</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="Z36" s="3" t="n"/>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -5859,72 +5812,73 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>21404</t>
+          <t xml:space="preserve">20782
+</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">11184
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">609
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6726
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">460
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1417
+          <t xml:space="preserve">1814
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">507
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">650
+          <t xml:space="preserve">685
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">676
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5936,66 +5890,67 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">1010
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">889
+</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38019
+</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">332
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">816
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">880
 </t>
         </is>
       </c>
-      <c r="T37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2169
-</t>
-        </is>
-      </c>
-      <c r="U37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">545
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1009
-</t>
-        </is>
-      </c>
-      <c r="W37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8371
-</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">848
-</t>
-        </is>
-      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3595
+          <t xml:space="preserve">4222
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">394
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6014,69 +5969,72 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4481
+          <t xml:space="preserve">4156
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>837</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">10351
+</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1665
+</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11702
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1137
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1135
 </t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">901
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n"/>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1130
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>414</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -6087,67 +6045,67 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 8
+          <t xml:space="preserve">02 4
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11276
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1 6 1
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -6166,139 +6124,143 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5799
+          <t xml:space="preserve">6244
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="n"/>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">051
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1025
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">012
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">108
+</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8157
+          <t xml:space="preserve">0625
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -6317,25 +6279,25 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
+          <t xml:space="preserve">6377
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -6347,17 +6309,21 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="n"/>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6366,91 +6332,91 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">695
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6469,39 +6435,44 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4512
+          <t xml:space="preserve">6993
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n"/>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6513,19 +6484,20 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 6
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -6542,61 +6514,61 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">1722
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4235
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">26417
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0198
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6615,49 +6587,49 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5294
+          <t xml:space="preserve">6088
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">11817
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113517
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -6669,84 +6641,94 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">046
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">2617
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1876
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2127
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">435
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="Y42" s="3" t="n"/>
-      <c r="Z42" s="3" t="n"/>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">610
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -6762,33 +6744,143 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="n"/>
+          <t xml:space="preserve">50494
+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
       <c r="F43" s="3" t="n"/>
-      <c r="G43" s="3" t="n"/>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n"/>
-      <c r="J43" s="3" t="n"/>
-      <c r="K43" s="3" t="n"/>
-      <c r="L43" s="3" t="n"/>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n"/>
-      <c r="O43" s="3" t="n"/>
-      <c r="P43" s="3" t="n"/>
-      <c r="Q43" s="3" t="n"/>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n"/>
-      <c r="T43" s="3" t="n"/>
-      <c r="U43" s="3" t="n"/>
-      <c r="V43" s="3" t="n"/>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
-      <c r="Y43" s="3" t="n"/>
-      <c r="Z43" s="3" t="n"/>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 279
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11227
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9720
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">398
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2109
+</t>
+        </is>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -6846,145 +6938,144 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19112
+          <t xml:space="preserve">31195
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10917
+          <t xml:space="preserve">1319
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">536
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">756
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">775
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">559
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">619
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3880
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2169
+          <t xml:space="preserve">21725
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8319
+          <t xml:space="preserve">1089
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">675
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008
+          <t xml:space="preserve">681
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12630
+          <t xml:space="preserve">3028
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23318
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -7003,135 +7094,140 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4178
+          <t xml:space="preserve">2239
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">11014
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">810154
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">621
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111819
+          <t xml:space="preserve">112138
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">11019
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1321
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">064
+          <t xml:space="preserve">0241
 </t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 47
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">541
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="n"/>
+          <t xml:space="preserve">598
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13654
+</t>
+        </is>
+      </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">218416
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="n"/>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18624
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -758,7 +758,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
@@ -794,7 +794,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -806,13 +806,13 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -830,7 +830,7 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">0178
 </t>
         </is>
       </c>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -885,13 +885,13 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146495
+          <t xml:space="preserve">4645
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -957,13 +957,13 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -975,13 +975,13 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -1017,13 +1017,14 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">760
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1047,37 +1048,37 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1095,19 +1096,19 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1942
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12561
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -1132,7 +1133,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -1162,19 +1163,19 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1193,7 +1194,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3537
+          <t xml:space="preserve">3557
 </t>
         </is>
       </c>
@@ -1265,7 +1266,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1283,7 +1284,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1295,7 +1296,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">770
 </t>
         </is>
       </c>
@@ -1307,7 +1308,7 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
@@ -1319,7 +1320,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -1331,7 +1332,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -1374,7 +1375,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">906
 </t>
         </is>
       </c>
@@ -1416,13 +1417,13 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1452,7 +1453,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -1507,7 +1508,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18252
+          <t xml:space="preserve">1825
 </t>
         </is>
       </c>
@@ -1519,8 +1520,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">713
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1547,7 +1547,12 @@
 </t>
         </is>
       </c>
-      <c r="J9" s="3" t="n"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">917
+</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">289
@@ -1562,25 +1567,25 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1598,13 +1603,13 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92856
+          <t xml:space="preserve">1986
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8911
+          <t xml:space="preserve">8918
 </t>
         </is>
       </c>
@@ -1616,13 +1621,13 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8712
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
@@ -1634,13 +1639,13 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94298
+          <t xml:space="preserve">94290
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -1659,7 +1664,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36501
+          <t xml:space="preserve">3650
 </t>
         </is>
       </c>
@@ -1683,7 +1688,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -1707,25 +1712,25 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -1737,13 +1742,13 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 2
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -1761,19 +1766,19 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">11914
 </t>
         </is>
       </c>
@@ -1816,25 +1821,25 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3296
+          <t xml:space="preserve">3246
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1333
+          <t xml:space="preserve">753
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1553
 </t>
         </is>
       </c>
@@ -1858,103 +1863,103 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">097
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1179
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11228
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2136
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1023
+</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12204
+</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">174
 </t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 316
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1023
-</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2899
-</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">720
-</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11886
+          <t xml:space="preserve">11586
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -1973,13 +1978,13 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5011
+          <t xml:space="preserve">5111
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -1991,7 +1996,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -2003,17 +2008,22 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01100
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">02
@@ -2022,55 +2032,55 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -2100,13 +2110,13 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">2810
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2125,7 +2135,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556
+          <t xml:space="preserve">4556
 </t>
         </is>
       </c>
@@ -2137,7 +2147,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
@@ -2149,7 +2159,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -2173,25 +2183,25 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -2203,7 +2213,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">982
 </t>
         </is>
       </c>
@@ -2215,19 +2225,18 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">18668
 </t>
         </is>
       </c>
@@ -2257,7 +2266,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">7260
 </t>
         </is>
       </c>
@@ -2282,7 +2291,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0329
+          <t xml:space="preserve">3319
 </t>
         </is>
       </c>
@@ -2300,13 +2309,13 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -2336,19 +2345,19 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -2360,7 +2369,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2384,13 +2393,13 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1711
+          <t xml:space="preserve">711
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
@@ -2402,19 +2411,19 @@
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2439,7 +2448,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4545
+          <t xml:space="preserve">4845
 </t>
         </is>
       </c>
@@ -2463,7 +2472,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -2475,19 +2484,19 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2505,13 +2514,13 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -2541,7 +2550,7 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2480
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
@@ -2565,7 +2574,7 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2577,7 +2586,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -2608,7 +2617,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6553
+          <t xml:space="preserve">652
 </t>
         </is>
       </c>
@@ -2620,7 +2629,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
@@ -2638,13 +2647,13 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1349
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -2656,31 +2665,25 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">662
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">706
-</t>
+          <t>456</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4930
-</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4320
+</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1157
 </t>
         </is>
       </c>
@@ -2704,31 +2707,31 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">2558
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">1909
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94210
+          <t xml:space="preserve">9210
 </t>
         </is>
       </c>
@@ -2753,31 +2756,31 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08141
+          <t xml:space="preserve">4614
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">21124
 </t>
         </is>
       </c>
@@ -2795,18 +2798,19 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1117
 </t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -2824,7 +2828,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
@@ -2842,7 +2846,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2860,13 +2864,13 @@
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1412
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">2014
 </t>
         </is>
       </c>
@@ -2890,7 +2894,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
@@ -2909,13 +2913,13 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9557
+          <t xml:space="preserve">3557
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2228
 </t>
         </is>
       </c>
@@ -2939,14 +2943,19 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n"/>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2964,19 +2973,19 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9828
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -2988,7 +2997,7 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12168
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
@@ -3006,25 +3015,25 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1740
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2102
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 7
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -3073,7 +3082,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1630
+          <t xml:space="preserve">2130
 </t>
         </is>
       </c>
@@ -3085,13 +3094,13 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
@@ -3103,13 +3112,13 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
@@ -3121,20 +3130,19 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -3145,7 +3153,7 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -3157,7 +3165,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1794
 </t>
         </is>
       </c>
@@ -3169,13 +3177,13 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
@@ -3187,7 +3195,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2889
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3218,7 +3226,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14979
+          <t xml:space="preserve">14179
 </t>
         </is>
       </c>
@@ -3230,7 +3238,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">11254
 </t>
         </is>
       </c>
@@ -3282,11 +3290,15 @@
 </t>
         </is>
       </c>
-      <c r="N20" s="3" t="n"/>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -3297,7 +3309,7 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -3315,43 +3327,43 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">8 0
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3370,7 +3382,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3713
+          <t xml:space="preserve">3793
 </t>
         </is>
       </c>
@@ -3382,7 +3394,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">0140
 </t>
         </is>
       </c>
@@ -3394,7 +3406,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -3406,7 +3418,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3418,7 +3430,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">2411
 </t>
         </is>
       </c>
@@ -3430,13 +3442,13 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3460,7 +3472,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -3478,7 +3490,7 @@
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -3490,23 +3502,28 @@
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="n"/>
+          <t xml:space="preserve">9181
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -3534,19 +3551,20 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">11132
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3581,7 +3599,7 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11209
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3593,43 +3611,43 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">2970
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 54
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -3647,7 +3665,7 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -3684,7 +3702,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11284
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
@@ -3702,7 +3720,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">614
 </t>
         </is>
       </c>
@@ -3714,8 +3732,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>013</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -3726,13 +3743,13 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">807
 </t>
         </is>
       </c>
@@ -3744,8 +3761,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -3754,7 +3770,12 @@
 </t>
         </is>
       </c>
-      <c r="P23" s="3" t="n"/>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1156
@@ -3763,19 +3784,20 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9185
+          <t xml:space="preserve">1915
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>32606</t>
+          <t xml:space="preserve">2328
+</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0498
+          <t xml:space="preserve">1498
 </t>
         </is>
       </c>
@@ -3793,7 +3815,7 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -3805,7 +3827,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1983
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
@@ -3824,13 +3846,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49129
+          <t xml:space="preserve">4179
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
+          <t xml:space="preserve">0236
 </t>
         </is>
       </c>
@@ -3842,19 +3864,19 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
@@ -3866,14 +3888,14 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">371
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -3885,7 +3907,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -3897,7 +3919,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0944
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -3921,7 +3943,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -3933,7 +3955,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -3945,7 +3967,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -3957,7 +3979,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -3976,19 +3998,19 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236
+          <t xml:space="preserve">2336
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 1
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -4000,7 +4022,8 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">76
+</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -4011,7 +4034,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
@@ -4023,25 +4046,25 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -4053,13 +4076,13 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -4083,37 +4106,36 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1719
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9208
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4132,7 +4154,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2683
+          <t xml:space="preserve">2283
 </t>
         </is>
       </c>
@@ -4156,13 +4178,13 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -4172,7 +4194,12 @@
 </t>
         </is>
       </c>
-      <c r="J26" s="3" t="n"/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">177
@@ -4193,19 +4220,19 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9088
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -4217,19 +4244,19 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -4247,28 +4274,18 @@
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1182
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">153
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="n"/>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">070
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -4284,7 +4301,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4358
+          <t xml:space="preserve">4356
 </t>
         </is>
       </c>
@@ -4308,7 +4325,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01312
+          <t xml:space="preserve">10122
 </t>
         </is>
       </c>
@@ -4320,7 +4337,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -4338,19 +4355,19 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">1735
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1088
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -4368,7 +4385,7 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -4384,16 +4401,20 @@
 </t>
         </is>
       </c>
-      <c r="T27" s="3" t="n"/>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">879
+</t>
+        </is>
+      </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -4454,7 +4475,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -4472,7 +4493,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -4496,7 +4517,7 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -4508,7 +4529,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
@@ -4532,19 +4553,19 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">481
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -4593,7 +4614,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091
+          <t xml:space="preserve">3097
 </t>
         </is>
       </c>
@@ -4605,20 +4626,25 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
@@ -4642,7 +4668,8 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t xml:space="preserve">1137
+</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4653,19 +4680,18 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>744</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -4683,13 +4709,13 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">661
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -4701,19 +4727,19 @@
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1358
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -4744,7 +4770,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15699
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -4768,13 +4794,13 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6459
+          <t xml:space="preserve">449
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">624
 </t>
         </is>
       </c>
@@ -4786,19 +4812,19 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">76 9
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">749
 </t>
         </is>
       </c>
@@ -4810,14 +4836,13 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4918
-</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="P30" s="3" t="n"/>
@@ -4835,7 +4860,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
@@ -4859,25 +4884,25 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8249
+          <t xml:space="preserve">824
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942280
+          <t xml:space="preserve">94280
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -4902,13 +4927,13 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -4932,7 +4957,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0815
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4942,12 +4967,7 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1150
@@ -4956,18 +4976,28 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="n"/>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16441
-</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="n"/>
+          <t xml:space="preserve">604
+</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001
+</t>
+        </is>
+      </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">199
@@ -4976,7 +5006,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
@@ -4988,19 +5018,19 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92116
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
+          <t xml:space="preserve">011
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
+          <t xml:space="preserve">17 0
 </t>
         </is>
       </c>
@@ -5010,7 +5040,12 @@
 </t>
         </is>
       </c>
-      <c r="X31" s="3" t="n"/>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">950
@@ -5019,7 +5054,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -5044,66 +5079,67 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2207
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>291</t>
+          <t xml:space="preserve">391
+</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">5716
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -5121,34 +5157,24 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="n"/>
       <c r="T32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">80
 </t>
         </is>
       </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">094
-</t>
-        </is>
-      </c>
+      <c r="U32" s="3" t="n"/>
       <c r="V32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1166
@@ -5163,19 +5189,19 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -5212,7 +5238,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">1817
 </t>
         </is>
       </c>
@@ -5224,19 +5250,19 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5248,19 +5274,19 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1601
+          <t xml:space="preserve">191619
 </t>
         </is>
       </c>
@@ -5290,49 +5316,49 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">718
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0165
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">28809
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -5357,13 +5383,13 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15719
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -5375,13 +5401,13 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -5393,13 +5419,13 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">023
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -5409,7 +5435,12 @@
 </t>
         </is>
       </c>
-      <c r="M34" s="3" t="n"/>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1
+</t>
+        </is>
+      </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">170
@@ -5418,7 +5449,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -5430,7 +5461,7 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5442,13 +5473,13 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
@@ -5466,7 +5497,7 @@
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
@@ -5478,7 +5509,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">1900
 </t>
         </is>
       </c>
@@ -5503,25 +5534,25 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">4778
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
@@ -5533,7 +5564,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -5563,11 +5594,16 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="n"/>
+          <t xml:space="preserve">1123
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">980
@@ -5576,13 +5612,13 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -5594,13 +5630,13 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">1 1 9
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">608
 </t>
         </is>
       </c>
@@ -5612,31 +5648,31 @@
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">1284
 </t>
         </is>
       </c>
@@ -5667,25 +5703,25 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -5709,25 +5745,25 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8708
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -5739,7 +5775,7 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -5757,13 +5793,13 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5787,13 +5823,13 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -5818,67 +5854,67 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11184
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">661
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">2922
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">3523
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">567
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">507
+          <t xml:space="preserve">5079
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">685
+          <t xml:space="preserve">683
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">676
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -5890,7 +5926,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5902,7 +5938,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">599
 </t>
         </is>
       </c>
@@ -5914,7 +5950,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38019
+          <t xml:space="preserve">3809
 </t>
         </is>
       </c>
@@ -5926,7 +5962,7 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">700
 </t>
         </is>
       </c>
@@ -5944,16 +5980,11 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4222
-</t>
-        </is>
-      </c>
-      <c r="Z37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4298
+</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="n"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5975,7 +6006,8 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>837</t>
+          <t xml:space="preserve">237
+</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -5992,31 +6024,31 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10351
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11702
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -6028,13 +6060,14 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>414</t>
+          <t xml:space="preserve">154
+</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -6045,7 +6078,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02 4
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
@@ -6057,55 +6090,55 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">762
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1176
 </t>
         </is>
       </c>
-      <c r="T38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 6 1
-</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1180
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -6124,7 +6157,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6244
+          <t xml:space="preserve">6243
 </t>
         </is>
       </c>
@@ -6136,7 +6169,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -6160,24 +6193,25 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
@@ -6189,13 +6223,14 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>910</t>
+          <t xml:space="preserve">910
+</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -6206,19 +6241,19 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -6236,19 +6271,19 @@
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">2715
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0625
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -6260,7 +6295,7 @@
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -6291,7 +6326,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -6303,13 +6338,14 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1653
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">153
+</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -6356,7 +6392,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6374,13 +6410,13 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
+          <t xml:space="preserve">19488
 </t>
         </is>
       </c>
@@ -6392,7 +6428,7 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -6416,7 +6452,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -6435,7 +6471,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6993
+          <t xml:space="preserve">6443
 </t>
         </is>
       </c>
@@ -6447,13 +6483,13 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -6464,15 +6500,10 @@
         </is>
       </c>
       <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
+      <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -6484,25 +6515,25 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1015
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -6520,55 +6551,55 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1722
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">9470
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26417
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">2390
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -6599,31 +6630,31 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">4709
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">1817
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -6635,31 +6666,31 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">046
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -6671,7 +6702,7 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -6681,42 +6712,37 @@
 </t>
         </is>
       </c>
-      <c r="S42" s="3" t="inlineStr">
+      <c r="S42" s="3" t="n"/>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">490
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">490
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="W42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">610
@@ -6725,7 +6751,7 @@
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -6744,7 +6770,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50494
+          <t xml:space="preserve">6044
 </t>
         </is>
       </c>
@@ -6756,14 +6782,19 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="n"/>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 279
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -6793,91 +6824,90 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1207
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2224
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91209
+</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2392
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1130
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11227
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9720
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">398
-</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2109
 </t>
         </is>
       </c>
@@ -6944,7 +6974,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
+          <t xml:space="preserve">1311
 </t>
         </is>
       </c>
@@ -6962,7 +6992,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">775
+          <t xml:space="preserve">772
 </t>
         </is>
       </c>
@@ -6980,43 +7010,42 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">1559
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">1619
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">94980
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -7034,19 +7063,20 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21725
+          <t xml:space="preserve">2825
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">798
+</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
@@ -7057,19 +7087,19 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">831
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">681
+          <t xml:space="preserve">106888
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3028
+          <t xml:space="preserve">23028
 </t>
         </is>
       </c>
@@ -7106,19 +7136,19 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11014
+          <t xml:space="preserve">11017
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810154
+          <t xml:space="preserve">1513
 </t>
         </is>
       </c>
@@ -7136,43 +7166,43 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">111119
 </t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112138
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11019
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">901
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0241
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -7184,35 +7214,40 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">585
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13654
+          <t xml:space="preserve">0654
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218416
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">160
@@ -7221,13 +7256,13 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1612
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
@@ -728,146 +728,122 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2891
-</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -885,146 +861,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4645
-</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1042,141 +994,118 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3380
-</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1942
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P6" s="3" t="n"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1194,146 +1123,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3557
-</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1351,146 +1256,122 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3779
-</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1508,14 +1389,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825
-</t>
+          <t>18252</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
-</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1525,128 +1404,107 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">615
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>841</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1033
-</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1986
-</t>
+          <t>956</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8918
-</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>955</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1664,146 +1522,122 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
-</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>111001</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11914
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1821,146 +1655,122 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3246
-</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">753
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1553
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11228
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12204
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11586
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1978,146 +1788,122 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2810
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2135,92 +1921,77 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4556
-</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
@@ -2230,50 +2001,42 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2291,146 +2054,122 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3319
-</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">711
-</t>
+          <t>711</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2448,146 +2187,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4845
-</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2605,68 +2320,57 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23069
-</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">652
-</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
-</t>
+          <t>957</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
-</t>
+          <t>489</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">669
-</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2676,69 +2380,58 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
-</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2558
-</t>
+          <t>558</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
-</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
+          <t>909</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>998</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9210
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2756,146 +2449,122 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4614
-</t>
+          <t>514</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>626</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2913,146 +2582,122 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3557
-</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
-</t>
+          <t>680</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3070,74 +2715,62 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
-</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -3147,68 +2780,57 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1794
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3226,74 +2848,62 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11254
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -3303,68 +2913,57 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 0
-</t>
+          <t>12 0</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3382,146 +2981,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3793
-</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2411
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
-</t>
+          <t>809</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9181
-</t>
+          <t>981</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3539,146 +3114,122 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089
-</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11132
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3696,38 +3247,32 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20894
-</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
-</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
+          <t>614</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
-</t>
+          <t>539</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3737,26 +3282,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">807
-</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -3766,69 +3307,58 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
-</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
-</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1915
-</t>
+          <t>915</t>
         </is>
       </c>
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2328
-</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1498
-</t>
+          <t>498</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
-</t>
+          <t>863</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3846,141 +3376,122 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0236
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3998,128 +3509,107 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2336
-</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
@@ -4129,14 +3619,12 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4154,135 +3642,113 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2283
-</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="X26" s="3" t="n"/>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z26" s="3" t="n"/>
@@ -4301,110 +3767,92 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10122
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1735
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
@@ -4414,32 +3862,27 @@
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4457,146 +3900,122 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3313
-</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
-</t>
+          <t>780</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4614,68 +4033,57 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3097
-</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -4685,74 +4093,62 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1358
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4770,74 +4166,62 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
-</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">449
-</t>
+          <t>449</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">624
-</t>
+          <t>624</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76 9
-</t>
+          <t>76 9</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4848,62 +4232,52 @@
       <c r="P30" s="3" t="n"/>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
-</t>
+          <t>994</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
-</t>
+          <t>892</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>851</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
-</t>
+          <t>824</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94280
-</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4921,141 +4295,118 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140
-</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">604
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
-</t>
+          <t>941</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">011
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 0
-</t>
+          <t>17 0</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5073,136 +4424,114 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3642
-</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
-</t>
+          <t>393</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="S32" s="3" t="n"/>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="U32" s="3" t="n"/>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5220,146 +4549,122 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191619
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28809
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5377,146 +4682,122 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114
-</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 1
-</t>
+          <t>115 0</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5534,146 +4815,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 1 9
-</t>
+          <t>8 9</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">608
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5691,146 +4948,122 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>718</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5848,140 +5081,117 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20782
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">661
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3523
-</t>
+          <t>523</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5079
-</t>
+          <t>501</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>771</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920
-</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
-</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">599
-</t>
+          <t>849</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3809
-</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">700
-</t>
+          <t>700</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
+          <t>816</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
-</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="Z37" s="3" t="n"/>
@@ -6000,146 +5210,122 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>859</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6157,146 +5343,122 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">012
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2715
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6314,146 +5476,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6377
-</t>
+          <t>377</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19488
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6471,136 +5609,114 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6443
-</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1015
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9470
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6618,141 +5734,118 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6088
-</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4709
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S42" s="3" t="n"/>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6770,98 +5863,82 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6044
-</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -6871,44 +5948,37 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2224
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91209
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6926,8 +5996,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -6968,44 +6037,37 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31195
-</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1311
-</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">536
-</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
-</t>
+          <t>775</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -7015,98 +6077,82 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1559
-</t>
+          <t>559</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1619
-</t>
+          <t>609</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94980
-</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
-</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
-</t>
+          <t>892</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>815</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2825
-</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
-</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
-</t>
+          <t>831</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106888
-</t>
+          <t>608</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23028
-</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7124,146 +6170,122 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239
-</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11017
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1513
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111119
-</t>
+          <t>1111111110</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>505</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0654
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1612
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>121</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>675</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>111001</t>
+          <t>0101</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>286</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>118</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>293</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>164</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1843,17 +1843,17 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>162</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>222</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>124</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>143</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="P16" s="3" t="n"/>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>993</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>982</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>198</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>185</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>980</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>144</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>154</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>141</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>262</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>656</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>183</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>172</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>71 2</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>93</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>180</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>131</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1168 2</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>904</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>149 1</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4376,17 +4376,17 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>916</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>17 0</t>
+          <t>17 04</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1815 0</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -4464,17 +4464,17 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>323</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>219</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>56</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>115 0</t>
+          <t>115 00</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>291</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>960</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>8 9</t>
+          <t>2 7 9</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>541</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>323</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>116</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3809 1</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>900</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>06</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>123</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>322</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>189</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>31195</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>659</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>260</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>507</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>1111111110</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>585</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/702/original_transcribed_data.xlsx
@@ -1070,7 +1070,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>154</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>34</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>377</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>171</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>18252</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>895</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>0101</t>
+          <t>210</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>888</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>511</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>301</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>223</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>998</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>254</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>118</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>561</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>12 0</t>
+          <t>02 0</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>508</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>184</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>173</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>173</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>71 2</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>179</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>139</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>1168 2</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -4346,17 +4346,17 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -4376,17 +4376,17 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>856</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>17 04</t>
+          <t>17 00</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>1815 0</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -4469,22 +4469,22 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>115</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>181</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>211</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>115 00</t>
+          <t>15 0</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>900</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>2 7 9</t>
+          <t>2 1 2 8</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>270</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>581</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>078</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>523</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>3809 1</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>158</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>488</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>228</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>149</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -6087,17 +6087,17 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>554</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>654</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>600</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>000</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>118</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>505</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
